--- a/outputs/06_技术分析记录.xlsx
+++ b/outputs/06_技术分析记录.xlsx
@@ -507,7 +507,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -522,17 +522,17 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>32.26</t>
+          <t>32.25</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>33.67</v>
+        <v>33.64</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>30.94</v>
+        <v>30.99</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>36.1</v>
+        <v>40.3</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -546,7 +546,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；RSI=36.1中性区</t>
+          <t>价格站上60日均线；RSI=40.3中性区</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -558,148 +558,148 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>300750</t>
+          <t>600900</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>长江电力</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>330.51</t>
+          <t>28.63</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>365.3</v>
+        <v>28.22</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>377.45</v>
+        <v>27.82</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>10.4</v>
+        <v>58.3</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>326.00</t>
+          <t>25.36</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>412.64</t>
+          <t>29.57</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=10.4超卖区；近20日已跌-16.1%，接近超跌</t>
+          <t>价格站上60日均线；MACD金叉；MACD红柱放大；RSI=58.3中性区</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望</t>
+          <t>中期趋势向上，可关注/持有</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>600900</t>
+          <t>300750</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>长江电力</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>28.45</t>
+          <t>337.11</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>28.19</v>
+        <v>362.16</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>27.78</v>
+        <v>376.27</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>56.2</v>
+        <v>20.8</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25.36</t>
+          <t>326.00</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29.57</t>
+          <t>412.64</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；MACD红柱放大；RSI=56.2中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=20.8超卖区；近20日已跌-15.7%，接近超跌</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有</t>
+          <t>趋势中性，观望</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>000333</t>
+          <t>600036</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>美的集团</t>
+          <t>招商银行</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>86.26</t>
+          <t>41.83</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>85.95</v>
+        <v>40.27</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>83.05</v>
+        <v>38.6</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>51.8</v>
+        <v>72.2</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72.28</t>
+          <t>34.28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89.50</t>
+          <t>41.83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；MACD红柱放大；RSI=51.8中性区</t>
+          <t>均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=72.2中性区</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -711,148 +711,148 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>600036</t>
+          <t>601318</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>招商银行</t>
+          <t>中国平安</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>54.73</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>40.09</v>
+        <v>54.47</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>38.51</v>
+        <v>51.93</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>68.2</v>
+        <v>53.8</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>34.28</t>
+          <t>45.92</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>41.78</t>
+          <t>58.01</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>均线多头排列(5&gt;10&gt;20&gt;60)；RSI=68.2中性区</t>
+          <t>价格站上60日均线；RSI=53.8中性区</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有</t>
+          <t>趋势中性，观望</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>002475</t>
+          <t>000333</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>美的集团</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>55.39</t>
+          <t>86.80</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>55.82</v>
+        <v>86.16</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>59.51</v>
+        <v>83.25</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>55.8</v>
+        <v>50.7</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>51.88</t>
+          <t>72.28</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>76.16</t>
+          <t>89.50</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=55.8中性区</t>
+          <t>价格站上60日均线；MACD红柱放大；RSI=50.7中性区</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望</t>
+          <t>中期趋势向上，可关注/持有</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>601318</t>
+          <t>600519</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>中国平安</t>
+          <t>贵州茅台</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>54.83</t>
+          <t>1277.96</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>54.27</v>
+        <v>1297.56</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>51.86</v>
+        <v>1277.22</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>54.9</v>
+        <v>38.3</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>45.92</t>
+          <t>1151.01</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>58.01</t>
+          <t>1363.35</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；MACD死叉；RSI=54.9中性区</t>
+          <t>价格站上60日均线；RSI=38.3中性区</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -864,51 +864,51 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>510300</t>
+          <t>588000</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>沪深300ETF</t>
+          <t>科创50ETF</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>4.66</v>
+        <v>1.72</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>4.75</v>
+        <v>1.88</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>41.2</v>
+        <v>39.6</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5.09</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；RSI=41.2中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；RSI=39.6中性区；近20日已跌-14.6%，接近超跌</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>趋势偏弱，回避或减仓</t>
+          <t>趋势中性，观望</t>
         </is>
       </c>
     </row>

--- a/outputs/06_技术分析记录.xlsx
+++ b/outputs/06_技术分析记录.xlsx
@@ -507,7 +507,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -522,17 +522,17 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>32.25</t>
+          <t>32.04</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>33.64</v>
+        <v>33.58</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>30.99</v>
+        <v>31.07</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>40.3</v>
+        <v>32.1</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -546,19 +546,19 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；RSI=40.3中性区</t>
+          <t>价格站上60日均线；RSI=32.1超卖区</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望</t>
+          <t>中期趋势向上，可关注/持有</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -573,17 +573,17 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>28.63</t>
+          <t>28.50</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>28.22</v>
+        <v>28.24</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>27.82</v>
+        <v>27.86</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>58.3</v>
+        <v>54.9</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -597,7 +597,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；MACD金叉；MACD红柱放大；RSI=58.3中性区</t>
+          <t>均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=54.9中性区</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -609,46 +609,46 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>300750</t>
+          <t>601318</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>中国平安</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>337.11</t>
+          <t>54.13</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>362.16</v>
+        <v>54.66</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>376.27</v>
+        <v>52.01</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>20.8</v>
+        <v>44.1</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>326.00</t>
+          <t>45.92</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>412.64</t>
+          <t>58.01</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=20.8超卖区；近20日已跌-15.7%，接近超跌</t>
+          <t>价格站上60日均线；RSI=44.1中性区</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -660,148 +660,148 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>600036</t>
+          <t>300750</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>招商银行</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>41.83</t>
+          <t>316.36</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>40.27</v>
+        <v>358.16</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>38.6</v>
+        <v>375.03</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>72.2</v>
+        <v>13.7</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34.28</t>
+          <t>316.00</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41.83</t>
+          <t>408.60</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=72.2中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；RSI=13.7超卖区；近20日已跌-20.2%，接近超跌</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有</t>
+          <t>趋势中性，观望</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>601318</t>
+          <t>000333</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>中国平安</t>
+          <t>美的集团</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>54.73</t>
+          <t>87.56</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>54.47</v>
+        <v>86.36</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>51.93</v>
+        <v>83.47</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>53.8</v>
+        <v>57.4</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>45.92</t>
+          <t>72.28</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>58.01</t>
+          <t>89.50</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；RSI=53.8中性区</t>
+          <t>价格站上60日均线；MACD红柱放大；RSI=57.4中性区</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望</t>
+          <t>中期趋势向上，可关注/持有</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>000333</t>
+          <t>600036</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>美的集团</t>
+          <t>招商银行</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>86.80</t>
+          <t>41.10</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>86.16</v>
+        <v>40.41</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>83.25</v>
+        <v>38.68</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>50.7</v>
+        <v>61.4</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>72.28</t>
+          <t>34.28</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>89.50</t>
+          <t>41.83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；MACD红柱放大；RSI=50.7中性区</t>
+          <t>均线多头排列(5&gt;10&gt;20&gt;60)；RSI=61.4中性区</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -813,46 +813,46 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>600519</t>
+          <t>002475</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>贵州茅台</t>
+          <t>立讯精密</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1277.96</t>
+          <t>51.63</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1297.56</v>
+        <v>55.21</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>1277.22</v>
+        <v>58.96</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>38.3</v>
+        <v>31.4</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1151.01</t>
+          <t>51.55</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1363.35</t>
+          <t>76.16</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；RSI=38.3中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；RSI=31.4超卖区</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -864,7 +864,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -879,17 +879,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>1.88</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>39.6</v>
+        <v>39.2</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；RSI=39.6中性区；近20日已跌-14.6%，接近超跌</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=39.2中性区；近20日已跌-13.2%，接近超跌</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">

--- a/outputs/06_技术分析记录.xlsx
+++ b/outputs/06_技术分析记录.xlsx
@@ -522,17 +522,17 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>32.04</t>
+          <t>31.68</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>33.58</v>
+        <v>33.56</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>31.07</v>
+        <v>31.06</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>32.1</v>
+        <v>30.4</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -546,7 +546,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；RSI=32.1超卖区</t>
+          <t>价格站上60日均线；RSI=30.4超卖区</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -624,17 +624,17 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>54.13</t>
+          <t>53.90</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>54.66</v>
+        <v>54.64</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>52.01</v>
+        <v>52</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>44.1</v>
+        <v>43</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -648,7 +648,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；RSI=44.1中性区</t>
+          <t>价格站上60日均线；RSI=43.0中性区</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -726,17 +726,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>87.56</t>
+          <t>87.23</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>86.36</v>
+        <v>86.34</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>83.47</v>
+        <v>83.45999999999999</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>57.4</v>
+        <v>55.5</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；MACD红柱放大；RSI=57.4中性区</t>
+          <t>价格站上60日均线；MACD红柱放大；RSI=55.5中性区</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">

--- a/outputs/06_技术分析记录.xlsx
+++ b/outputs/06_技术分析记录.xlsx
@@ -507,7 +507,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -522,17 +522,17 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>31.68</t>
+          <t>32.17</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>33.56</v>
+        <v>33.55</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>31.06</v>
+        <v>31.15</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>30.4</v>
+        <v>34</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -546,7 +546,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；RSI=30.4超卖区</t>
+          <t>价格站上60日均线；MACD红柱放大；RSI=34.0超卖区</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -558,7 +558,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -573,17 +573,17 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>28.50</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
         <v>28.24</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>27.86</v>
+        <v>27.91</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>54.9</v>
+        <v>57.1</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -597,7 +597,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=54.9中性区</t>
+          <t>均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=57.1中性区</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -609,46 +609,46 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>601318</t>
+          <t>300750</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>中国平安</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>53.90</t>
+          <t>305.48</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>54.64</v>
+        <v>353.99</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>52</v>
+        <v>373.55</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>45.92</t>
+          <t>299.00</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>58.01</t>
+          <t>408.60</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；RSI=43.0中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；RSI=13.0超卖区；5日均量为60日均量的1.32倍，量能放大；近20日已跌-21.5%，接近超跌</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -660,46 +660,46 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>300750</t>
+          <t>601318</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>中国平安</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>316.36</t>
+          <t>53.51</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>358.16</v>
+        <v>54.77</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>375.03</v>
+        <v>52.09</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>13.7</v>
+        <v>42.4</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>316.00</t>
+          <t>45.92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>408.60</t>
+          <t>58.01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；RSI=13.7超卖区；近20日已跌-20.2%，接近超跌</t>
+          <t>价格站上60日均线；RSI=42.4中性区</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -711,7 +711,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -726,21 +726,21 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>87.23</t>
+          <t>85.00</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>86.34</v>
+        <v>86.36</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>83.45999999999999</v>
+        <v>83.67</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>55.5</v>
+        <v>43.9</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>72.28</t>
+          <t>72.48</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -750,109 +750,109 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；MACD红柱放大；RSI=55.5中性区</t>
+          <t>价格站上60日均线；RSI=43.9中性区</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有</t>
+          <t>趋势中性，观望</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>600036</t>
+          <t>002475</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>招商银行</t>
+          <t>立讯精密</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>41.10</t>
+          <t>52.89</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>40.41</v>
+        <v>55.18</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>38.68</v>
+        <v>58.59</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>61.4</v>
+        <v>36.5</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34.28</t>
+          <t>51.00</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41.83</t>
+          <t>75.66</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>均线多头排列(5&gt;10&gt;20&gt;60)；RSI=61.4中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=36.5中性区</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有</t>
+          <t>趋势中性，观望</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>002475</t>
+          <t>600036</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>招商银行</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>51.63</t>
+          <t>40.92</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>55.21</v>
+        <v>40.5</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>58.96</v>
+        <v>38.76</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>31.4</v>
+        <v>61.9</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>51.55</t>
+          <t>34.28</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76.16</t>
+          <t>41.83</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；RSI=31.4超卖区</t>
+          <t>均线多头排列(5&gt;10&gt;20&gt;60)；MACD死叉；RSI=61.9中性区</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -864,7 +864,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -879,17 +879,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>39.2</v>
+        <v>39.6</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=39.2中性区；近20日已跌-13.2%，接近超跌</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD金叉；MACD红柱放大；RSI=39.6中性区</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">

--- a/outputs/06_技术分析记录.xlsx
+++ b/outputs/06_技术分析记录.xlsx
@@ -507,7 +507,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -522,17 +522,17 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>32.17</t>
+          <t>31.68</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>33.55</v>
+        <v>33.56</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>31.15</v>
+        <v>31.06</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>34</v>
+        <v>30.4</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -546,7 +546,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；MACD红柱放大；RSI=34.0超卖区</t>
+          <t>价格站上60日均线；RSI=30.4超卖区</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -558,7 +558,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -573,17 +573,17 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.50</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
         <v>28.24</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>27.91</v>
+        <v>27.86</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>57.1</v>
+        <v>54.9</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -597,7 +597,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=57.1中性区</t>
+          <t>均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=54.9中性区</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -609,46 +609,46 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>300750</t>
+          <t>601318</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>中国平安</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>305.48</t>
+          <t>53.90</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>353.99</v>
+        <v>54.64</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>373.55</v>
+        <v>52</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>299.00</t>
+          <t>45.92</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>408.60</t>
+          <t>58.01</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；RSI=13.0超卖区；5日均量为60日均量的1.32倍，量能放大；近20日已跌-21.5%，接近超跌</t>
+          <t>价格站上60日均线；RSI=43.0中性区</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -660,46 +660,46 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>601318</t>
+          <t>300750</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>中国平安</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>53.51</t>
+          <t>316.36</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>54.77</v>
+        <v>358.16</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>52.09</v>
+        <v>375.03</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>42.4</v>
+        <v>13.7</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45.92</t>
+          <t>316.00</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>58.01</t>
+          <t>408.60</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；RSI=42.4中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；RSI=13.7超卖区；近20日已跌-20.2%，接近超跌</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -711,7 +711,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -726,21 +726,21 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>85.00</t>
+          <t>87.23</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>86.36</v>
+        <v>86.34</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>83.67</v>
+        <v>83.45999999999999</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>43.9</v>
+        <v>55.5</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>72.48</t>
+          <t>72.28</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -750,109 +750,109 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；RSI=43.9中性区</t>
+          <t>价格站上60日均线；MACD红柱放大；RSI=55.5中性区</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望</t>
+          <t>中期趋势向上，可关注/持有</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>002475</t>
+          <t>600036</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>招商银行</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>52.89</t>
+          <t>41.10</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>55.18</v>
+        <v>40.41</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>58.59</v>
+        <v>38.68</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>36.5</v>
+        <v>61.4</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>51.00</t>
+          <t>34.28</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>75.66</t>
+          <t>41.83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=36.5中性区</t>
+          <t>均线多头排列(5&gt;10&gt;20&gt;60)；RSI=61.4中性区</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望</t>
+          <t>中期趋势向上，可关注/持有</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>600036</t>
+          <t>002475</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>招商银行</t>
+          <t>立讯精密</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>40.92</t>
+          <t>51.63</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>40.5</v>
+        <v>55.21</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>38.76</v>
+        <v>58.96</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>61.9</v>
+        <v>31.4</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>34.28</t>
+          <t>51.55</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>41.83</t>
+          <t>76.16</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>均线多头排列(5&gt;10&gt;20&gt;60)；MACD死叉；RSI=61.9中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；RSI=31.4超卖区</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -864,7 +864,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -879,17 +879,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>39.6</v>
+        <v>39.2</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD金叉；MACD红柱放大；RSI=39.6中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=39.2中性区；近20日已跌-13.2%，接近超跌</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">

--- a/outputs/06_技术分析记录.xlsx
+++ b/outputs/06_技术分析记录.xlsx
@@ -507,7 +507,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -522,17 +522,17 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>32.17</t>
+          <t>30.90</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>33.55</v>
+        <v>33.41</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>31.15</v>
+        <v>31.25</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>34</v>
+        <v>28.5</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -546,121 +546,121 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；MACD红柱放大；RSI=34.0超卖区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；RSI=28.5超卖区</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有</t>
+          <t>趋势中性，观望</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>600900</t>
+          <t>300750</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>长江电力</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>304.30</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>28.24</v>
+        <v>349.95</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>27.91</v>
+        <v>371.95</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>57.1</v>
+        <v>13.5</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>25.36</t>
+          <t>299.00</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>29.57</t>
+          <t>408.60</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=57.1中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；RSI=13.5超卖区；5日均量为60日均量的1.35倍，量能放大；近20日已跌-21.0%，接近超跌</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有</t>
+          <t>趋势中性，观望</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>300750</t>
+          <t>600900</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>长江电力</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>305.48</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>353.99</v>
+        <v>28.26</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>373.55</v>
+        <v>27.96</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>13</v>
+        <v>58.2</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>299.00</t>
+          <t>25.36</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>408.60</t>
+          <t>29.57</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；RSI=13.0超卖区；5日均量为60日均量的1.32倍，量能放大；近20日已跌-21.5%，接近超跌</t>
+          <t>均线多头排列(5&gt;10&gt;20&gt;60)；RSI=58.2中性区</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望</t>
+          <t>中期趋势向上，可关注/持有</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -675,17 +675,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>53.51</t>
+          <t>53.35</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>54.77</v>
+        <v>54.87</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>52.09</v>
+        <v>52.17</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>42.4</v>
+        <v>41.7</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -699,7 +699,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；RSI=42.4中性区</t>
+          <t>价格站上60日均线；RSI=41.7中性区</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -711,7 +711,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -726,21 +726,21 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>85.00</t>
+          <t>85.04</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>86.36</v>
+        <v>86.34</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>83.67</v>
+        <v>83.87</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>43.9</v>
+        <v>43.8</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>72.48</t>
+          <t>72.89</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；RSI=43.9中性区</t>
+          <t>价格站上60日均线；RSI=43.8中性区</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -762,46 +762,46 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>002475</t>
+          <t>600036</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>招商银行</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>52.89</t>
+          <t>40.60</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>55.18</v>
+        <v>40.58</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>58.59</v>
+        <v>38.85</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>36.5</v>
+        <v>60.9</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>51.00</t>
+          <t>34.28</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>75.66</t>
+          <t>41.83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=36.5中性区</t>
+          <t>价格站上60日均线；RSI=60.9中性区</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -813,97 +813,97 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>600036</t>
+          <t>002475</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>招商银行</t>
+          <t>立讯精密</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>40.92</t>
+          <t>52.13</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>40.5</v>
+        <v>55.12</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>38.76</v>
+        <v>58.22</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>61.9</v>
+        <v>36.1</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>34.28</t>
+          <t>51.00</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>41.83</t>
+          <t>71.36</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>均线多头排列(5&gt;10&gt;20&gt;60)；MACD死叉；RSI=61.9中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；RSI=36.1中性区</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望</t>
+          <t>趋势偏弱，回避或减仓</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>588000</t>
+          <t>510300</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>科创50ETF</t>
+          <t>沪深300ETF</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>4.53</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1.7</v>
+        <v>4.62</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>1.87</v>
+        <v>4.72</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>39.6</v>
+        <v>23.5</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>4.49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>5.05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD金叉；MACD红柱放大；RSI=39.6中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；RSI=23.5超卖区</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">

--- a/outputs/06_技术分析记录.xlsx
+++ b/outputs/06_技术分析记录.xlsx
@@ -563,46 +563,46 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>300750</t>
+          <t>600900</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>长江电力</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>304.30</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>349.95</v>
+        <v>28.26</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>371.95</v>
+        <v>27.96</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>13.5</v>
+        <v>58.2</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>299.00</t>
+          <t>25.36</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>408.60</t>
+          <t>29.57</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；RSI=13.5超卖区；5日均量为60日均量的1.35倍，量能放大；近20日已跌-21.0%，接近超跌</t>
+          <t>均线多头排列(5&gt;10&gt;20&gt;60)；RSI=58.2中性区</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望</t>
+          <t>中期趋势向上，可关注/持有</t>
         </is>
       </c>
     </row>
@@ -614,46 +614,46 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>600900</t>
+          <t>601318</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>长江电力</t>
+          <t>中国平安</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>53.35</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>28.26</v>
+        <v>54.87</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>27.96</v>
+        <v>52.17</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>58.2</v>
+        <v>41.7</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25.36</t>
+          <t>45.92</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29.57</t>
+          <t>58.01</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>均线多头排列(5&gt;10&gt;20&gt;60)；RSI=58.2中性区</t>
+          <t>价格站上60日均线；RSI=41.7中性区</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有</t>
+          <t>趋势中性，观望</t>
         </is>
       </c>
     </row>
@@ -665,41 +665,41 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>601318</t>
+          <t>300750</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>中国平安</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>53.35</t>
+          <t>304.30</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>54.87</v>
+        <v>349.96</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>52.17</v>
+        <v>371.95</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>41.7</v>
+        <v>13.5</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45.92</t>
+          <t>299.00</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>58.01</t>
+          <t>408.60</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；RSI=41.7中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；RSI=13.5超卖区；近20日已跌-21.0%，接近超跌</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">

--- a/outputs/06_技术分析记录.xlsx
+++ b/outputs/06_技术分析记录.xlsx
@@ -563,46 +563,46 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>600900</t>
+          <t>300750</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>长江电力</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>304.30</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>28.26</v>
+        <v>349.95</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>27.96</v>
+        <v>371.95</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>58.2</v>
+        <v>13.5</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>25.36</t>
+          <t>299.00</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>29.57</t>
+          <t>408.60</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>均线多头排列(5&gt;10&gt;20&gt;60)；RSI=58.2中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；RSI=13.5超卖区；5日均量为60日均量的1.35倍，量能放大；近20日已跌-21.0%，接近超跌</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有</t>
+          <t>趋势中性，观望</t>
         </is>
       </c>
     </row>
@@ -614,46 +614,46 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>601318</t>
+          <t>600900</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>中国平安</t>
+          <t>长江电力</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>53.35</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>54.87</v>
+        <v>28.26</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>52.17</v>
+        <v>27.96</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>41.7</v>
+        <v>58.2</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>45.92</t>
+          <t>25.36</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>58.01</t>
+          <t>29.57</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；RSI=41.7中性区</t>
+          <t>均线多头排列(5&gt;10&gt;20&gt;60)；RSI=58.2中性区</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望</t>
+          <t>中期趋势向上，可关注/持有</t>
         </is>
       </c>
     </row>
@@ -665,41 +665,41 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>300750</t>
+          <t>601318</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>中国平安</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>304.30</t>
+          <t>53.35</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>349.96</v>
+        <v>54.87</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>371.95</v>
+        <v>52.17</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>13.5</v>
+        <v>41.7</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>299.00</t>
+          <t>45.92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>408.60</t>
+          <t>58.01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；RSI=13.5超卖区；近20日已跌-21.0%，接近超跌</t>
+          <t>价格站上60日均线；RSI=41.7中性区</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">

--- a/outputs/06_技术分析记录.xlsx
+++ b/outputs/06_技术分析记录.xlsx
@@ -507,7 +507,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -522,17 +522,17 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>30.90</t>
+          <t>31.41</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>33.41</v>
+        <v>33.24</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>31.25</v>
+        <v>31.36</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>28.5</v>
+        <v>36.3</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -546,19 +546,19 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；RSI=28.5超卖区</t>
+          <t>价格站上60日均线；MACD红柱放大；RSI=36.3中性区</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望</t>
+          <t>中期趋势向上，可关注/持有</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -573,17 +573,17 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>304.30</t>
+          <t>301.95</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>349.95</v>
+        <v>345.49</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>371.95</v>
+        <v>370.66</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>13.5</v>
+        <v>13.9</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -597,7 +597,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；RSI=13.5超卖区；5日均量为60日均量的1.35倍，量能放大；近20日已跌-21.0%，接近超跌</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=13.9超卖区；5日均量为60日均量的1.42倍，量能放大；近20日已跌-22.8%，接近超跌</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -609,148 +609,148 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>600900</t>
+          <t>601318</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>长江电力</t>
+          <t>中国平安</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>53.37</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>28.26</v>
+        <v>54.92</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>27.96</v>
+        <v>52.29</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>58.2</v>
+        <v>42</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25.36</t>
+          <t>45.92</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29.57</t>
+          <t>58.01</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>均线多头排列(5&gt;10&gt;20&gt;60)；RSI=58.2中性区</t>
+          <t>价格站上60日均线；RSI=42.0中性区</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有</t>
+          <t>趋势中性，观望</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>601318</t>
+          <t>000333</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>中国平安</t>
+          <t>美的集团</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>53.35</t>
+          <t>84.40</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>54.87</v>
+        <v>86.34</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>52.17</v>
+        <v>84.03</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>41.7</v>
+        <v>31</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45.92</t>
+          <t>73.62</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>58.01</t>
+          <t>89.50</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；RSI=41.7中性区</t>
+          <t>价格站上60日均线；RSI=31.0超卖区</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望</t>
+          <t>中期趋势向上，可关注/持有</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>000333</t>
+          <t>600900</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>美的集团</t>
+          <t>长江电力</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>85.04</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>86.34</v>
+        <v>28.27</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>83.87</v>
+        <v>28</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>43.8</v>
+        <v>53.4</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>72.89</t>
+          <t>25.47</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>89.50</t>
+          <t>29.57</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；RSI=43.8中性区</t>
+          <t>价格站上60日均线；RSI=53.4中性区</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -762,46 +762,46 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>600036</t>
+          <t>002475</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>招商银行</t>
+          <t>立讯精密</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>40.60</t>
+          <t>54.10</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>40.58</v>
+        <v>55.09</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>38.85</v>
+        <v>58</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>60.9</v>
+        <v>39.7</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34.28</t>
+          <t>51.00</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41.83</t>
+          <t>70.74</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；RSI=60.9中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=39.7中性区</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -813,58 +813,58 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>002475</t>
+          <t>600036</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>招商银行</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>52.13</t>
+          <t>40.59</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>55.12</v>
+        <v>40.67</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>58.22</v>
+        <v>38.95</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>36.1</v>
+        <v>54.7</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>51.00</t>
+          <t>34.28</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71.36</t>
+          <t>41.83</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；RSI=36.1中性区</t>
+          <t>价格站上60日均线；RSI=54.7中性区</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>趋势偏弱，回避或减仓</t>
+          <t>趋势中性，观望</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -879,17 +879,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
         <v>4.62</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>4.72</v>
+        <v>4.71</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>23.5</v>
+        <v>34</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；RSI=23.5超卖区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=34.0超卖区</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">

--- a/outputs/06_技术分析记录.xlsx
+++ b/outputs/06_技术分析记录.xlsx
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>345.49</v>
+        <v>345.5</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>370.66</v>
@@ -597,7 +597,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=13.9超卖区；5日均量为60日均量的1.42倍，量能放大；近20日已跌-22.8%，接近超跌</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=13.9超卖区；5日均量为60日均量的1.34倍，量能放大；近20日已跌-22.8%，接近超跌</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">

--- a/outputs/06_技术分析记录.xlsx
+++ b/outputs/06_技术分析记录.xlsx
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>345.5</v>
+        <v>345.49</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>370.66</v>
@@ -597,7 +597,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=13.9超卖区；5日均量为60日均量的1.34倍，量能放大；近20日已跌-22.8%，接近超跌</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=13.9超卖区；5日均量为60日均量的1.42倍，量能放大；近20日已跌-22.8%，接近超跌</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">

--- a/outputs/06_技术分析记录.xlsx
+++ b/outputs/06_技术分析记录.xlsx
@@ -507,97 +507,97 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>601899</t>
+          <t>300750</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>紫金矿业</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>31.41</t>
+          <t>297.10</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>33.24</v>
+        <v>340.95</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>31.36</v>
+        <v>369.09</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>36.3</v>
+        <v>14</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>24.00</t>
+          <t>295.50</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>35.47</t>
+          <t>408.60</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；MACD红柱放大；RSI=36.3中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=14.0超卖区；5日均量为60日均量的1.56倍，量能放大；近20日已跌-23.4%，接近超跌</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有</t>
+          <t>趋势中性，观望</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>300750</t>
+          <t>601899</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>紫金矿业</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>301.95</t>
+          <t>31.30</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>345.49</v>
+        <v>33.08</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>370.66</v>
+        <v>31.46</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>13.9</v>
+        <v>35.3</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>299.00</t>
+          <t>24.00</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>408.60</t>
+          <t>35.47</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=13.9超卖区；5日均量为60日均量的1.42倍，量能放大；近20日已跌-22.8%，接近超跌</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=35.3中性区</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -624,21 +624,21 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>53.37</t>
+          <t>53.98</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>54.92</v>
+        <v>54.93</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>52.29</v>
+        <v>52.4</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>42</v>
+        <v>36.4</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>45.92</t>
+          <t>46.21</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -648,58 +648,58 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；RSI=42.0中性区</t>
+          <t>价格站上60日均线；MACD红柱放大；RSI=36.4中性区</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望</t>
+          <t>中期趋势向上，可关注/持有</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>000333</t>
+          <t>600036</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>美的集团</t>
+          <t>招商银行</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>84.40</t>
+          <t>41.04</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>86.34</v>
+        <v>40.74</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>84.03</v>
+        <v>39.04</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>31</v>
+        <v>51.9</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73.62</t>
+          <t>34.28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89.50</t>
+          <t>41.83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；RSI=31.0超卖区</t>
+          <t>价格站上60日均线；MACD红柱放大；RSI=51.9中性区</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -711,7 +711,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -726,21 +726,21 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>28.10</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
         <v>28.27</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>28</v>
+        <v>28.03</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>53.4</v>
+        <v>44</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25.47</t>
+          <t>25.57</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；RSI=53.4中性区</t>
+          <t>均线多头排列(5&gt;10&gt;20&gt;60)；MACD死叉；RSI=44.0中性区</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -762,7 +762,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -777,17 +777,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>54.10</t>
+          <t>54.44</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>55.09</v>
+        <v>55.12</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>58</v>
+        <v>57.82</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>39.7</v>
+        <v>42.6</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=39.7中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=42.6中性区</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -813,46 +813,46 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>600036</t>
+          <t>000333</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>招商银行</t>
+          <t>美的集团</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>40.59</t>
+          <t>80.90</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>40.67</v>
+        <v>86.09</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>38.95</v>
+        <v>84.09</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>54.7</v>
+        <v>22.6</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>34.28</t>
+          <t>73.62</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>41.83</t>
+          <t>89.50</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；RSI=54.7中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；RSI=22.6超卖区</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -864,7 +864,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
@@ -889,7 +889,7 @@
         <v>4.71</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=34.0超卖区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD金叉；MACD红柱放大；RSI=39.0中性区</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">

--- a/outputs/06_技术分析记录.xlsx
+++ b/outputs/06_技术分析记录.xlsx
@@ -507,7 +507,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -522,17 +522,17 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>297.10</t>
+          <t>304.63</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>340.95</v>
+        <v>337.35</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>369.09</v>
+        <v>367.64</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>14</v>
+        <v>23.5</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -546,7 +546,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=14.0超卖区；5日均量为60日均量的1.56倍，量能放大；近20日已跌-23.4%，接近超跌</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=23.5超卖区；5日均量为60日均量的1.54倍，量能放大；近20日已跌-19.1%，接近超跌</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -558,7 +558,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -573,17 +573,17 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>31.30</t>
+          <t>31.41</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>33.08</v>
+        <v>32.97</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>31.46</v>
+        <v>31.57</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>35.3</v>
+        <v>39.9</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -597,7 +597,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=35.3中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=39.9中性区</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -624,17 +624,17 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>53.98</t>
+          <t>54.46</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>54.93</v>
+        <v>54.95</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>52.4</v>
+        <v>52.53</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>36.4</v>
+        <v>42.8</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -648,7 +648,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；MACD红柱放大；RSI=36.4中性区</t>
+          <t>价格站上60日均线；MACD红柱放大；RSI=42.8中性区</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -660,97 +660,97 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>600036</t>
+          <t>002475</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>招商银行</t>
+          <t>立讯精密</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>41.04</t>
+          <t>54.84</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>40.74</v>
+        <v>55.12</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>39.04</v>
+        <v>57.56</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>51.9</v>
+        <v>43.4</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34.28</t>
+          <t>51.00</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41.83</t>
+          <t>70.63</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；MACD红柱放大；RSI=51.9中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD金叉；MACD红柱放大；RSI=43.4中性区</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有</t>
+          <t>趋势中性，观望</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>600900</t>
+          <t>600036</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>长江电力</t>
+          <t>招商银行</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>28.10</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>28.27</v>
+        <v>40.81</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>28.03</v>
+        <v>39.15</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>44</v>
+        <v>49.5</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25.57</t>
+          <t>34.28</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29.57</t>
+          <t>41.83</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>均线多头排列(5&gt;10&gt;20&gt;60)；MACD死叉；RSI=44.0中性区</t>
+          <t>价格站上60日均线；RSI=49.5中性区</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -762,46 +762,46 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>002475</t>
+          <t>600900</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>长江电力</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>54.44</t>
+          <t>28.02</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>55.12</v>
+        <v>28.26</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>57.82</v>
+        <v>28.07</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>42.6</v>
+        <v>34.5</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>51.00</t>
+          <t>25.57</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>70.74</t>
+          <t>29.57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=42.6中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；RSI=34.5超卖区</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -813,46 +813,46 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>000333</t>
+          <t>600519</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>美的集团</t>
+          <t>贵州茅台</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>80.90</t>
+          <t>1253.80</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>86.09</v>
+        <v>1286.68</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>84.09</v>
+        <v>1284.79</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>22.6</v>
+        <v>33.8</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73.62</t>
+          <t>1166.33</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89.50</t>
+          <t>1363.35</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；RSI=22.6超卖区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=33.8超卖区</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -864,7 +864,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -883,13 +883,13 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>4.62</v>
+        <v>4.61</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>4.71</v>
+        <v>4.7</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>39</v>
+        <v>48.8</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD金叉；MACD红柱放大；RSI=39.0中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=48.8中性区</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">

--- a/outputs/06_技术分析记录.xlsx
+++ b/outputs/06_技术分析记录.xlsx
@@ -507,58 +507,58 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>300750</t>
+          <t>601318</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>中国平安</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>304.63</t>
+          <t>53.87</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>337.35</v>
+        <v>54.88</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>367.64</v>
+        <v>52.62</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>23.5</v>
+        <v>28.9</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>295.50</t>
+          <t>47.33</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>408.60</t>
+          <t>58.01</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=23.5超卖区；5日均量为60日均量的1.54倍，量能放大；近20日已跌-19.1%，接近超跌</t>
+          <t>价格站上60日均线；MACD红柱放大；RSI=28.9超卖区</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望</t>
+          <t>中期趋势向上，可关注/持有</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -577,17 +577,17 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>32.97</v>
+        <v>32.81</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>31.57</v>
+        <v>31.68</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>39.9</v>
+        <v>36.9</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>24.00</t>
+          <t>25.10</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -597,7 +597,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=39.9中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=36.9中性区</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -609,58 +609,58 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>601318</t>
+          <t>300750</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>中国平安</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>54.46</t>
+          <t>301.00</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>54.95</v>
+        <v>333.45</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>52.53</v>
+        <v>366.28</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>42.8</v>
+        <v>21.4</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>46.21</t>
+          <t>295.50</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>58.01</t>
+          <t>408.60</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；MACD红柱放大；RSI=42.8中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=21.4超卖区；近20日已跌-20.6%，接近超跌</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有</t>
+          <t>趋势中性，观望</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -675,17 +675,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>54.84</t>
+          <t>54.37</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>55.12</v>
+        <v>54.99</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>57.56</v>
+        <v>57.36</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>43.4</v>
+        <v>44.5</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -694,12 +694,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>70.63</t>
+          <t>65.83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD金叉；MACD红柱放大；RSI=43.4中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=44.5中性区</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -711,7 +711,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -726,21 +726,21 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.60</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>40.81</v>
+        <v>40.85</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>39.15</v>
+        <v>39.24</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>49.5</v>
+        <v>45.2</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>34.28</t>
+          <t>35.13</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；RSI=49.5中性区</t>
+          <t>价格站上60日均线；RSI=45.2中性区</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -762,46 +762,46 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>600900</t>
+          <t>000333</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>长江电力</t>
+          <t>美的集团</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>28.02</t>
+          <t>82.47</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>28.26</v>
+        <v>85.69</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>28.07</v>
+        <v>84.29000000000001</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>34.5</v>
+        <v>31.5</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25.57</t>
+          <t>76.98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29.57</t>
+          <t>89.50</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；RSI=34.5超卖区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=31.5超卖区</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -813,7 +813,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -828,21 +828,21 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1253.80</t>
+          <t>1251.24</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1286.68</v>
+        <v>1284.1</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>1284.79</v>
+        <v>1285.76</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>33.8</v>
+        <v>32.5</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1166.33</t>
+          <t>1170.28</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -852,7 +852,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=33.8超卖区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=32.5超卖区</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -864,7 +864,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -879,17 +879,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
         <v>4.61</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>4.7</v>
+        <v>4.69</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>48.8</v>
+        <v>45</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -898,12 +898,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=48.8中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=45.0中性区</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">

--- a/outputs/06_技术分析记录.xlsx
+++ b/outputs/06_技术分析记录.xlsx
@@ -507,109 +507,109 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>601318</t>
+          <t>601899</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>中国平安</t>
+          <t>紫金矿业</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>53.87</t>
+          <t>30.01</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>54.88</v>
+        <v>32.59</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>52.62</v>
+        <v>31.75</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>28.9</v>
+        <v>30.6</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>47.33</t>
+          <t>26.13</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>58.01</t>
+          <t>35.47</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；MACD红柱放大；RSI=28.9超卖区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；RSI=30.6超卖区；近20日已跌-13.2%，接近超跌</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有</t>
+          <t>趋势中性，观望</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>601899</t>
+          <t>601318</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>紫金矿业</t>
+          <t>中国平安</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>31.41</t>
+          <t>53.25</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>32.81</v>
+        <v>54.8</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>31.68</v>
+        <v>52.7</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>36.9</v>
+        <v>24.4</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>25.10</t>
+          <t>47.33</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>35.47</t>
+          <t>58.01</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=36.9中性区</t>
+          <t>价格站上60日均线；RSI=24.4超卖区</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望</t>
+          <t>中期趋势向上，可关注/持有</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -624,21 +624,21 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>301.00</t>
+          <t>293.50</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>333.45</v>
+        <v>329.47</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>366.28</v>
+        <v>364.83</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>21.4</v>
+        <v>18.4</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>295.50</t>
+          <t>293.00</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=21.4超卖区；近20日已跌-20.6%，接近超跌</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=18.4超卖区；近20日已跌-21.3%，接近超跌</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -660,58 +660,58 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>002475</t>
+          <t>600900</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>长江电力</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>54.37</t>
+          <t>28.36</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>54.99</v>
+        <v>28.27</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>57.36</v>
+        <v>28.15</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>44.5</v>
+        <v>48.7</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51.00</t>
+          <t>25.99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65.83</t>
+          <t>29.57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=44.5中性区</t>
+          <t>价格站上60日均线；MACD红柱放大；RSI=48.7中性区</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望</t>
+          <t>中期趋势向上，可关注/持有</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -726,21 +726,21 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>40.60</t>
+          <t>40.69</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>40.85</v>
+        <v>40.9</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>39.24</v>
+        <v>39.33</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>45.2</v>
+        <v>38.6</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>35.13</t>
+          <t>35.35</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；RSI=45.2中性区</t>
+          <t>价格站上60日均线；RSI=38.6中性区</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -762,7 +762,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -777,21 +777,21 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>82.47</t>
+          <t>82.65</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>85.69</v>
+        <v>85.51000000000001</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>84.29000000000001</v>
+        <v>84.39</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>31.5</v>
+        <v>30.8</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>76.98</t>
+          <t>77.31</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=31.5超卖区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=30.8超卖区</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -813,58 +813,58 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>600519</t>
+          <t>002475</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>贵州茅台</t>
+          <t>立讯精密</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1251.24</t>
+          <t>52.00</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1284.1</v>
+        <v>54.73</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>1285.76</v>
+        <v>57.22</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>32.5</v>
+        <v>43.2</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1170.28</t>
+          <t>51.00</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1363.35</t>
+          <t>65.83</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=32.5超卖区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；RSI=43.2中性区</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望</t>
+          <t>趋势偏弱，回避或减仓</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -879,17 +879,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>4.51</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>4.61</v>
+        <v>4.6</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>4.69</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>45</v>
+        <v>36.7</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -898,17 +898,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=45.0中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；RSI=36.7中性区</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望</t>
+          <t>趋势偏弱，回避或减仓</t>
         </is>
       </c>
     </row>

--- a/outputs/06_技术分析记录.xlsx
+++ b/outputs/06_技术分析记录.xlsx
@@ -507,7 +507,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -522,17 +522,17 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>30.01</t>
+          <t>29.42</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>32.59</v>
+        <v>32.32</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>31.75</v>
+        <v>31.79</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>30.6</v>
+        <v>30.2</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -546,7 +546,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；RSI=30.6超卖区；近20日已跌-13.2%，接近超跌</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；RSI=30.2超卖区；近20日已跌-15.1%，接近超跌</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -558,46 +558,46 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>601318</t>
+          <t>600900</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>中国平安</t>
+          <t>长江电力</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>53.25</t>
+          <t>28.55</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>54.8</v>
+        <v>28.29</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>52.7</v>
+        <v>28.18</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>24.4</v>
+        <v>68.2</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>47.33</t>
+          <t>25.99</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>58.01</t>
+          <t>29.57</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；RSI=24.4超卖区</t>
+          <t>价格站上60日均线；MACD金叉；MACD红柱放大；RSI=68.2中性区</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -624,21 +624,21 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>293.50</t>
+          <t>291.99</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>329.47</v>
+        <v>325.65</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>364.83</v>
+        <v>363.38</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>18.4</v>
+        <v>18.6</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>293.00</t>
+          <t>286.66</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=18.4超卖区；近20日已跌-21.3%，接近超跌</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=18.6超卖区；近20日已跌-20.8%，接近超跌</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -660,58 +660,58 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>600900</t>
+          <t>601318</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>长江电力</t>
+          <t>中国平安</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>28.36</t>
+          <t>52.40</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>28.27</v>
+        <v>54.68</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>28.15</v>
+        <v>52.78</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>48.7</v>
+        <v>28.1</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25.99</t>
+          <t>47.52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29.57</t>
+          <t>58.01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；MACD红柱放大；RSI=48.7中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；RSI=28.1超卖区</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有</t>
+          <t>趋势中性，观望</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -726,21 +726,21 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>40.69</t>
+          <t>40.64</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>40.9</v>
+        <v>40.97</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>39.33</v>
+        <v>39.41</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>38.6</v>
+        <v>44.4</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>35.35</t>
+          <t>35.52</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；RSI=38.6中性区</t>
+          <t>价格站上60日均线；RSI=44.4中性区</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -762,7 +762,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -777,21 +777,21 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>82.65</t>
+          <t>82.00</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>85.51000000000001</v>
+        <v>85.3</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>84.39</v>
+        <v>84.45</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>30.8</v>
+        <v>32.4</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>77.31</t>
+          <t>77.86</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=30.8超卖区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=32.4超卖区</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -813,97 +813,97 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>002475</t>
+          <t>600519</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>贵州茅台</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>52.00</t>
+          <t>1243.88</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>54.73</v>
+        <v>1278.66</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>57.22</v>
+        <v>1287.15</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>43.2</v>
+        <v>17.8</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>51.00</t>
+          <t>1170.28</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>65.83</t>
+          <t>1363.35</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；RSI=43.2中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=17.8超卖区</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>趋势偏弱，回避或减仓</t>
+          <t>趋势中性，观望</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>510300</t>
+          <t>588000</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>沪深300ETF</t>
+          <t>科创50ETF</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4.51</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>4.6</v>
+        <v>1.7</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>4.69</v>
+        <v>1.81</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>36.7</v>
+        <v>41.8</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4.49</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；RSI=36.7中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；RSI=41.8中性区</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">

--- a/outputs/06_技术分析记录.xlsx
+++ b/outputs/06_技术分析记录.xlsx
@@ -507,7 +507,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -522,17 +522,17 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>29.42</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>32.32</v>
+        <v>32.12</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>31.79</v>
+        <v>31.81</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>30.2</v>
+        <v>22.6</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -546,7 +546,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；RSI=30.2超卖区；近20日已跌-15.1%，接近超跌</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=22.6超卖区；近20日已跌-12.2%，接近超跌</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -558,148 +558,148 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>600900</t>
+          <t>300750</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>长江电力</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>28.55</t>
+          <t>286.80</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>28.29</v>
+        <v>321.81</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>28.18</v>
+        <v>361.94</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>68.2</v>
+        <v>20.3</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>25.99</t>
+          <t>285.74</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>29.57</t>
+          <t>408.60</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；MACD金叉；MACD红柱放大；RSI=68.2中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=20.3超卖区；近20日已跌-21.1%，接近超跌</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有</t>
+          <t>趋势中性，观望</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>300750</t>
+          <t>600900</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>长江电力</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>291.99</t>
+          <t>28.45</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>325.65</v>
+        <v>28.31</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>363.38</v>
+        <v>28.22</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>18.6</v>
+        <v>64.5</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>286.66</t>
+          <t>26.26</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>408.60</t>
+          <t>29.57</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=18.6超卖区；近20日已跌-20.8%，接近超跌</t>
+          <t>价格站上60日均线；MACD红柱放大；RSI=64.5中性区</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望</t>
+          <t>中期趋势向上，可关注/持有</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>601318</t>
+          <t>002475</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>中国平安</t>
+          <t>立讯精密</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>52.40</t>
+          <t>50.40</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>54.68</v>
+        <v>54.03</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>52.78</v>
+        <v>56.77</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>28.1</v>
+        <v>36.3</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47.52</t>
+          <t>49.30</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>58.01</t>
+          <t>65.52</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；RSI=28.1超卖区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；RSI=36.3中性区；近20日已跌-12.5%，接近超跌</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -711,46 +711,46 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>600036</t>
+          <t>601318</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>招商银行</t>
+          <t>中国平安</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>40.64</t>
+          <t>52.57</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>40.97</v>
+        <v>54.57</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>39.41</v>
+        <v>52.83</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>44.4</v>
+        <v>33</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>35.52</t>
+          <t>47.52</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>41.83</t>
+          <t>58.01</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；RSI=44.4中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；RSI=33.0超卖区</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -762,46 +762,46 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>000333</t>
+          <t>600036</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>美的集团</t>
+          <t>招商银行</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>82.00</t>
+          <t>40.51</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>85.3</v>
+        <v>40.99</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>84.45</v>
+        <v>39.47</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>32.4</v>
+        <v>44.8</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>77.86</t>
+          <t>36.15</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>89.50</t>
+          <t>41.83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=32.4超卖区</t>
+          <t>价格站上60日均线；RSI=44.8中性区</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -813,46 +813,46 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>600519</t>
+          <t>000333</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>贵州茅台</t>
+          <t>美的集团</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1243.88</t>
+          <t>81.67</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1278.66</v>
+        <v>84.98999999999999</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>1287.15</v>
+        <v>84.48</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>17.8</v>
+        <v>34.7</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1170.28</t>
+          <t>77.86</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1363.35</t>
+          <t>89.50</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=17.8超卖区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=34.7超卖区</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -864,51 +864,51 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>588000</t>
+          <t>510300</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>科创50ETF</t>
+          <t>沪深300ETF</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1.7</v>
+        <v>4.58</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>1.81</v>
+        <v>4.67</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>41.8</v>
+        <v>29</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>4.40</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；RSI=41.8中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；RSI=29.0超卖区</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>趋势偏弱，回避或减仓</t>
+          <t>趋势中性，观望</t>
         </is>
       </c>
     </row>

--- a/outputs/06_技术分析记录.xlsx
+++ b/outputs/06_技术分析记录.xlsx
@@ -522,17 +522,17 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>29.46</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>32.12</v>
+        <v>32.11</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>31.81</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>22.6</v>
+        <v>21.7</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -546,7 +546,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=22.6超卖区；近20日已跌-12.2%，接近超跌</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；RSI=21.7超卖区；近20日已跌-12.5%，接近超跌</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -624,17 +624,17 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>28.45</t>
+          <t>28.38</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>28.31</v>
+        <v>28.3</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>28.22</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>64.5</v>
+        <v>62.3</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -648,7 +648,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；MACD红柱放大；RSI=64.5中性区</t>
+          <t>价格站上60日均线；MACD红柱放大；RSI=62.3中性区</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -726,17 +726,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>52.57</t>
+          <t>52.50</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>54.57</v>
+        <v>54.56</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>52.83</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>33</v>
+        <v>32.2</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；RSI=33.0超卖区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；RSI=32.2超卖区</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>81.67</t>
+          <t>81.66</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
@@ -879,7 +879,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>4.42</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
@@ -889,7 +889,7 @@
         <v>4.67</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>29</v>
+        <v>26.9</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；RSI=29.0超卖区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；RSI=26.9超卖区</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">

--- a/outputs/06_技术分析记录.xlsx
+++ b/outputs/06_技术分析记录.xlsx
@@ -507,7 +507,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -522,17 +522,17 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>29.46</t>
+          <t>29.79</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>32.11</v>
+        <v>31.92</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>31.81</v>
+        <v>31.86</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>21.7</v>
+        <v>19.6</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -546,7 +546,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；RSI=21.7超卖区；近20日已跌-12.5%，接近超跌</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=19.6超卖区</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -558,58 +558,58 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>300750</t>
+          <t>601318</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>中国平安</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>286.80</t>
+          <t>53.29</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>321.81</v>
+        <v>54.41</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>361.94</v>
+        <v>52.92</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>20.3</v>
+        <v>34.6</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>285.74</t>
+          <t>47.52</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>408.60</t>
+          <t>58.01</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=20.3超卖区；近20日已跌-21.1%，接近超跌</t>
+          <t>价格站上60日均线；MACD红柱放大；RSI=34.6超卖区</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望</t>
+          <t>中期趋势向上，可关注/持有</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -624,21 +624,21 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>28.38</t>
+          <t>28.54</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>28.3</v>
+        <v>28.31</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>28.22</v>
+        <v>28.25</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>62.3</v>
+        <v>62</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26.26</t>
+          <t>26.46</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；MACD红柱放大；RSI=62.3中性区</t>
+          <t>均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=62.0中性区</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -660,46 +660,46 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>002475</t>
+          <t>300750</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>50.40</t>
+          <t>291.11</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>54.03</v>
+        <v>318.46</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>56.77</v>
+        <v>360.61</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>36.3</v>
+        <v>23.1</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49.30</t>
+          <t>285.74</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65.52</t>
+          <t>408.60</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；RSI=36.3中性区；近20日已跌-12.5%，接近超跌</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=23.1超卖区；近20日已跌-18.7%，接近超跌</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -711,46 +711,46 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>601318</t>
+          <t>002475</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>中国平安</t>
+          <t>立讯精密</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>52.50</t>
+          <t>49.43</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>54.56</v>
+        <v>53.66</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>52.83</v>
+        <v>56.54</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>32.2</v>
+        <v>31.3</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>47.52</t>
+          <t>49.04</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>58.01</t>
+          <t>65.52</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；RSI=32.2超卖区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；RSI=31.3超卖区；近20日已跌-13.2%，接近超跌</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -762,7 +762,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -777,17 +777,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>40.51</t>
+          <t>41.26</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>40.99</v>
+        <v>41.01</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>39.47</v>
+        <v>39.55</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>44.8</v>
+        <v>52.9</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；RSI=44.8中性区</t>
+          <t>价格站上60日均线；MACD红柱放大；RSI=52.9中性区</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望</t>
+          <t>中期趋势向上，可关注/持有</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -828,17 +828,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>81.66</t>
+          <t>80.10</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>84.98999999999999</v>
+        <v>84.62</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>84.48</v>
+        <v>84.5</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>34.7</v>
+        <v>25.5</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=34.7超卖区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；RSI=25.5超卖区</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -864,7 +864,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -879,17 +879,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4.42</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>4.58</v>
+        <v>4.56</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>4.67</v>
+        <v>4.66</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>26.9</v>
+        <v>27.4</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；RSI=26.9超卖区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；RSI=27.4超卖区</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">

--- a/outputs/06_技术分析记录.xlsx
+++ b/outputs/06_技术分析记录.xlsx
@@ -507,7 +507,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -522,17 +522,17 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>29.79</t>
+          <t>29.37</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>31.92</v>
+        <v>31.74</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>31.86</v>
+        <v>31.9</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>19.6</v>
+        <v>19.2</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -546,7 +546,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=19.6超卖区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=19.2超卖区</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -558,46 +558,46 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>601318</t>
+          <t>600900</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>中国平安</t>
+          <t>长江电力</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>53.29</t>
+          <t>28.90</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>54.41</v>
+        <v>28.32</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>52.92</v>
+        <v>28.28</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>34.6</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>47.52</t>
+          <t>26.74</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>58.01</t>
+          <t>29.57</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；MACD红柱放大；RSI=34.6超卖区</t>
+          <t>均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=67.1中性区</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -609,97 +609,97 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>600900</t>
+          <t>300750</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>长江电力</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>28.54</t>
+          <t>286.75</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>28.31</v>
+        <v>315.38</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>28.25</v>
+        <v>359.4</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>62</v>
+        <v>20.9</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26.46</t>
+          <t>285.17</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29.57</t>
+          <t>408.60</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=62.0中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=20.9超卖区；近20日已跌-17.7%，接近超跌</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有</t>
+          <t>趋势中性，观望</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>300750</t>
+          <t>002475</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>立讯精密</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>291.11</t>
+          <t>48.43</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>318.46</v>
+        <v>53.23</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>360.61</v>
+        <v>56.31</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>23.1</v>
+        <v>32.1</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>285.74</t>
+          <t>47.90</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>408.60</t>
+          <t>65.52</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=23.1超卖区；近20日已跌-18.7%，接近超跌</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；RSI=32.1超卖区；近20日已跌-15.2%，接近超跌</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -711,46 +711,46 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>002475</t>
+          <t>601318</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>中国平安</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>49.43</t>
+          <t>52.67</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>53.66</v>
+        <v>54.26</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>56.54</v>
+        <v>52.98</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>31.3</v>
+        <v>29.2</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>49.04</t>
+          <t>47.52</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>65.52</t>
+          <t>58.01</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；RSI=31.3超卖区；近20日已跌-13.2%，接近超跌</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=29.2超卖区</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -762,7 +762,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -777,21 +777,21 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>41.26</t>
+          <t>41.71</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>41.01</v>
+        <v>41.05</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>39.55</v>
+        <v>39.63</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>52.9</v>
+        <v>51.6</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>36.33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；MACD红柱放大；RSI=52.9中性区</t>
+          <t>价格站上60日均线；MACD红柱放大；RSI=51.6中性区</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -813,7 +813,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -828,17 +828,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>80.10</t>
+          <t>81.74</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>84.62</v>
+        <v>84.36</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>84.5</v>
+        <v>84.54000000000001</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>25.5</v>
+        <v>33.5</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；RSI=25.5超卖区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=33.5超卖区</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -864,7 +864,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -879,21 +879,21 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>4.56</v>
+        <v>4.55</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>4.66</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>27.4</v>
+        <v>26.1</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4.40</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；RSI=27.4超卖区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；RSI=26.1超卖区</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">

--- a/outputs/06_技术分析记录.xlsx
+++ b/outputs/06_技术分析记录.xlsx
@@ -507,160 +507,160 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>601899</t>
+          <t>300750</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>紫金矿业</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>29.37</t>
+          <t>297.64</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>31.74</v>
+        <v>312.79</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>31.9</v>
+        <v>358.12</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>19.2</v>
+        <v>32</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>26.13</t>
+          <t>285.17</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>35.47</t>
+          <t>408.60</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=19.2超卖区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD金叉；MACD红柱放大；RSI=32.0超卖区；近20日已跌-14.8%，接近超跌</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望</t>
+          <t>中期趋势向上，可关注/持有</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>600900</t>
+          <t>601899</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>长江电力</t>
+          <t>紫金矿业</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>28.90</t>
+          <t>30.83</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>28.32</v>
+        <v>31.61</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>28.28</v>
+        <v>31.96</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>67.09999999999999</v>
+        <v>40.2</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>26.74</t>
+          <t>26.32</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>29.57</t>
+          <t>35.47</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=67.1中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=40.2中性区</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有</t>
+          <t>趋势中性，观望</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>300750</t>
+          <t>600900</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>长江电力</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>286.75</t>
+          <t>28.98</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>315.38</v>
+        <v>28.35</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>359.4</v>
+        <v>28.31</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>20.9</v>
+        <v>62.7</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>285.17</t>
+          <t>26.81</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>408.60</t>
+          <t>29.57</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=20.9超卖区；近20日已跌-17.7%，接近超跌</t>
+          <t>均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=62.7中性区</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望</t>
+          <t>中期趋势向上，可关注/持有</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -675,21 +675,21 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>48.43</t>
+          <t>47.59</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>53.23</v>
+        <v>52.8</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>56.31</v>
+        <v>56.03</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>32.1</v>
+        <v>26.6</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47.90</t>
+          <t>46.02</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；RSI=32.1超卖区；近20日已跌-15.2%，接近超跌</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；RSI=26.6超卖区；近20日已跌-15.3%，接近超跌</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -711,148 +711,148 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>601318</t>
+          <t>600036</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>中国平安</t>
+          <t>招商银行</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>52.67</t>
+          <t>41.42</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>54.26</v>
+        <v>41.07</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>52.98</v>
+        <v>39.71</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>29.2</v>
+        <v>50.8</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>47.52</t>
+          <t>36.33</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>58.01</t>
+          <t>42.09</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=29.2超卖区</t>
+          <t>价格站上60日均线；MACD红柱放大；RSI=50.8中性区</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望</t>
+          <t>中期趋势向上，可关注/持有</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>600036</t>
+          <t>600519</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>招商银行</t>
+          <t>贵州茅台</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>41.71</t>
+          <t>1263.00</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>41.05</v>
+        <v>1269.54</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>39.63</v>
+        <v>1291.08</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>51.6</v>
+        <v>44.6</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36.33</t>
+          <t>1170.28</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41.83</t>
+          <t>1363.35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；MACD红柱放大；RSI=51.6中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD金叉；MACD红柱放大；RSI=44.6中性区</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有</t>
+          <t>趋势中性，观望</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>000333</t>
+          <t>601318</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>美的集团</t>
+          <t>中国平安</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>81.74</t>
+          <t>52.94</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>84.36</v>
+        <v>54.06</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>84.54000000000001</v>
+        <v>53.06</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>33.5</v>
+        <v>35.3</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77.86</t>
+          <t>47.52</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89.50</t>
+          <t>58.01</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=33.5超卖区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=35.3中性区</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -864,7 +864,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -883,17 +883,17 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>4.55</v>
+        <v>4.54</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>4.66</v>
+        <v>4.65</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>26.1</v>
+        <v>28.8</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；RSI=26.1超卖区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=28.8超卖区</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">

--- a/outputs/06_技术分析记录.xlsx
+++ b/outputs/06_技术分析记录.xlsx
@@ -522,17 +522,17 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>297.64</t>
+          <t>297.75</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>312.79</v>
+        <v>312.8</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>358.12</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>32</v>
+        <v>32.1</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -546,7 +546,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD金叉；MACD红柱放大；RSI=32.0超卖区；近20日已跌-14.8%，接近超跌</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD金叉；MACD红柱放大；RSI=32.1超卖区；近20日已跌-14.8%，接近超跌</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>30.83</t>
+          <t>30.80</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -583,7 +583,7 @@
         <v>31.96</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>40.2</v>
+        <v>40</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -597,7 +597,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=40.2中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=40.0中性区</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -624,7 +624,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>28.98</t>
+          <t>28.99</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
@@ -634,7 +634,7 @@
         <v>28.31</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>62.7</v>
+        <v>62.9</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -648,7 +648,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=62.7中性区</t>
+          <t>均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=62.9中性区</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -716,46 +716,46 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>600036</t>
+          <t>601318</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>招商银行</t>
+          <t>中国平安</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>41.42</t>
+          <t>52.83</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>41.07</v>
+        <v>54.05</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>39.71</v>
+        <v>53.06</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>50.8</v>
+        <v>34.2</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>36.33</t>
+          <t>47.52</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>42.09</t>
+          <t>58.01</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；MACD红柱放大；RSI=50.8中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=34.2超卖区</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有</t>
+          <t>趋势中性，观望</t>
         </is>
       </c>
     </row>
@@ -767,46 +767,46 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>600519</t>
+          <t>600036</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>贵州茅台</t>
+          <t>招商银行</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1263.00</t>
+          <t>41.42</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1269.54</v>
+        <v>41.07</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>1291.08</v>
+        <v>39.71</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>44.6</v>
+        <v>50.8</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1170.28</t>
+          <t>36.33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1363.35</t>
+          <t>42.09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD金叉；MACD红柱放大；RSI=44.6中性区</t>
+          <t>价格站上60日均线；MACD红柱放大；RSI=50.8中性区</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望</t>
+          <t>中期趋势向上，可关注/持有</t>
         </is>
       </c>
     </row>
@@ -818,41 +818,41 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>601318</t>
+          <t>600519</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>中国平安</t>
+          <t>贵州茅台</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>52.94</t>
+          <t>1263.00</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>54.06</v>
+        <v>1269.54</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>53.06</v>
+        <v>1291.08</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>35.3</v>
+        <v>44.6</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>47.52</t>
+          <t>1170.28</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>58.01</t>
+          <t>1363.35</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=35.3中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD金叉；MACD红柱放大；RSI=44.6中性区</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
@@ -889,7 +889,7 @@
         <v>4.65</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>28.8</v>
+        <v>28.1</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=28.8超卖区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；RSI=28.1超卖区</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">

--- a/outputs/06_技术分析记录.xlsx
+++ b/outputs/06_技术分析记录.xlsx
@@ -507,46 +507,46 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>300750</t>
+          <t>600036</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>招商银行</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>297.75</t>
+          <t>42.76</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>312.8</v>
+        <v>41.12</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>358.12</v>
+        <v>39.81</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>32.1</v>
+        <v>58.9</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>285.17</t>
+          <t>36.71</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>408.60</t>
+          <t>42.76</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD金叉；MACD红柱放大；RSI=32.1超卖区；近20日已跌-14.8%，接近超跌</t>
+          <t>均线多头排列(5&gt;10&gt;20&gt;60)；MACD金叉；MACD红柱放大；RSI=58.9中性区</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -558,7 +558,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -573,17 +573,17 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>30.80</t>
+          <t>30.22</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>31.61</v>
+        <v>31.46</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>31.96</v>
+        <v>32.01</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>40</v>
+        <v>37.1</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -597,7 +597,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=40.0中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=37.1中性区</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -624,21 +624,21 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>28.99</t>
+          <t>29.38</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="F4" s="2" t="n">
         <v>28.35</v>
       </c>
-      <c r="F4" s="2" t="n">
-        <v>28.31</v>
-      </c>
       <c r="G4" s="2" t="n">
-        <v>62.9</v>
+        <v>66.2</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26.81</t>
+          <t>27.01</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=62.9中性区</t>
+          <t>均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=66.2中性区</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -660,97 +660,97 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>002475</t>
+          <t>601318</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>中国平安</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>47.59</t>
+          <t>53.24</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>52.8</v>
+        <v>53.85</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>56.03</v>
+        <v>53.14</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>26.6</v>
+        <v>38.8</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46.02</t>
+          <t>47.52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65.52</t>
+          <t>58.01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；RSI=26.6超卖区；近20日已跌-15.3%，接近超跌</t>
+          <t>价格站上60日均线；MACD红柱放大；RSI=38.8中性区</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望</t>
+          <t>中期趋势向上，可关注/持有</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>601318</t>
+          <t>300750</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>中国平安</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>52.83</t>
+          <t>298.38</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>54.05</v>
+        <v>310.17</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>53.06</v>
+        <v>357.31</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>34.2</v>
+        <v>27.4</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>47.52</t>
+          <t>285.17</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>58.01</t>
+          <t>408.60</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=34.2超卖区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=27.4超卖区；近20日已跌-15.0%，接近超跌</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -762,97 +762,97 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>600036</t>
+          <t>002475</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>招商银行</t>
+          <t>立讯精密</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>41.42</t>
+          <t>46.32</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>41.07</v>
+        <v>52.4</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>39.71</v>
+        <v>55.77</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>50.8</v>
+        <v>29</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36.33</t>
+          <t>46.02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42.09</t>
+          <t>64.20</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；MACD红柱放大；RSI=50.8中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；RSI=29.0超卖区；近20日已跌-14.7%，接近超跌</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有</t>
+          <t>趋势中性，观望</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>600519</t>
+          <t>000333</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>贵州茅台</t>
+          <t>美的集团</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1263.00</t>
+          <t>83.50</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1269.54</v>
+        <v>83.92</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>1291.08</v>
+        <v>84.66</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>44.6</v>
+        <v>38.8</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1170.28</t>
+          <t>78.30</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1363.35</t>
+          <t>89.50</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD金叉；MACD红柱放大；RSI=44.6中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=38.8中性区</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -864,7 +864,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -879,17 +879,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>4.54</v>
+        <v>4.53</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>4.65</v>
+        <v>4.64</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>28.1</v>
+        <v>28.2</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -898,12 +898,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；RSI=28.1超卖区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；RSI=28.2超卖区</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">

--- a/outputs/06_技术分析记录.xlsx
+++ b/outputs/06_技术分析记录.xlsx
@@ -507,199 +507,199 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>600036</t>
+          <t>601899</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>招商银行</t>
+          <t>紫金矿业</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>42.76</t>
+          <t>30.40</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>41.12</v>
+        <v>31.33</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>39.81</v>
+        <v>32.06</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>58.9</v>
+        <v>41.4</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>36.71</t>
+          <t>26.33</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>42.76</t>
+          <t>35.47</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>均线多头排列(5&gt;10&gt;20&gt;60)；MACD金叉；MACD红柱放大；RSI=58.9中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=41.4中性区</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有</t>
+          <t>趋势中性，观望</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>601899</t>
+          <t>600900</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>紫金矿业</t>
+          <t>长江电力</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>30.22</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>31.46</v>
+        <v>28.46</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>32.01</v>
+        <v>28.38</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>37.1</v>
+        <v>63.5</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>26.32</t>
+          <t>27.34</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>35.47</t>
+          <t>29.57</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=37.1中性区</t>
+          <t>均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=63.5中性区</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望</t>
+          <t>中期趋势向上，可关注/持有</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>600900</t>
+          <t>300750</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>长江电力</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>29.38</t>
+          <t>289.10</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>28.4</v>
+        <v>307.21</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>28.35</v>
+        <v>356.17</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>66.2</v>
+        <v>31.6</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27.01</t>
+          <t>285.17</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29.57</t>
+          <t>408.60</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=66.2中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=31.6超卖区；近20日已跌-17.0%，接近超跌</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有</t>
+          <t>趋势中性，观望</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>601318</t>
+          <t>600036</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>中国平安</t>
+          <t>招商银行</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>53.24</t>
+          <t>42.80</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>53.85</v>
+        <v>41.21</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>53.14</v>
+        <v>39.9</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>38.8</v>
+        <v>68.7</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47.52</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>58.01</t>
+          <t>42.95</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；MACD红柱放大；RSI=38.8中性区</t>
+          <t>均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=68.7中性区</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -711,46 +711,46 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>300750</t>
+          <t>002475</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>立讯精密</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>298.38</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>310.17</v>
+        <v>51.91</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>357.31</v>
+        <v>55.56</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>27.4</v>
+        <v>30.9</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>285.17</t>
+          <t>44.70</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>408.60</t>
+          <t>64.20</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=27.4超卖区；近20日已跌-15.0%，接近超跌</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；RSI=30.9超卖区；近20日已跌-17.5%，接近超跌</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -762,46 +762,46 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>002475</t>
+          <t>601318</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>中国平安</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>46.32</t>
+          <t>51.69</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>52.4</v>
+        <v>53.67</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>55.77</v>
+        <v>53.19</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>46.02</t>
+          <t>47.52</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>64.20</t>
+          <t>58.01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；RSI=29.0超卖区；近20日已跌-14.7%，接近超跌</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；RSI=35.0超卖区</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -813,7 +813,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -828,17 +828,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>83.50</t>
+          <t>82.79</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>83.92</v>
+        <v>83.75</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>84.66</v>
+        <v>84.7</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>38.8</v>
+        <v>35.2</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=38.8中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=35.2中性区</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -864,7 +864,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -879,21 +879,21 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>4.53</v>
+        <v>4.51</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>4.64</v>
+        <v>4.63</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>28.2</v>
+        <v>29.1</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；RSI=28.2超卖区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=29.1超卖区</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">

--- a/outputs/06_技术分析记录.xlsx
+++ b/outputs/06_技术分析记录.xlsx
@@ -507,7 +507,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -522,21 +522,21 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>30.40</t>
+          <t>29.98</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>31.33</v>
+        <v>31.14</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>32.06</v>
+        <v>32.09</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>41.4</v>
+        <v>35.2</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>26.33</t>
+          <t>27.50</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -546,7 +546,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=41.4中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=35.2中性区</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -558,7 +558,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -573,17 +573,17 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.45</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>28.46</v>
+        <v>28.54</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>28.38</v>
+        <v>28.4</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>63.5</v>
+        <v>68.5</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -597,7 +597,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=63.5中性区</t>
+          <t>均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=68.5中性区</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -609,109 +609,109 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>300750</t>
+          <t>600036</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>招商银行</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>289.10</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>307.21</v>
+        <v>41.29</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>356.17</v>
+        <v>39.99</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>31.6</v>
+        <v>69.5</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>285.17</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>408.60</t>
+          <t>42.95</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=31.6超卖区；近20日已跌-17.0%，接近超跌</t>
+          <t>均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=69.5中性区</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望</t>
+          <t>中期趋势向上，可关注/持有</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>600036</t>
+          <t>300750</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>招商银行</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>42.80</t>
+          <t>280.12</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>41.21</v>
+        <v>304.44</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>39.9</v>
+        <v>354.79</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>68.7</v>
+        <v>32.5</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>280.12</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42.95</t>
+          <t>408.60</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=68.7中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；RSI=32.5超卖区；近20日已跌-16.5%，接近超跌</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有</t>
+          <t>趋势中性，观望</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -726,17 +726,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>44.94</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>51.91</v>
+        <v>51.4</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>55.56</v>
+        <v>55.28</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>30.9</v>
+        <v>22.3</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；RSI=30.9超卖区；近20日已跌-17.5%，接近超跌</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；RSI=22.3超卖区；近20日已跌-18.4%，接近超跌</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -762,46 +762,46 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>601318</t>
+          <t>000333</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>中国平安</t>
+          <t>美的集团</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>51.69</t>
+          <t>83.70</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>53.67</v>
+        <v>83.67</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>53.19</v>
+        <v>84.73999999999999</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>35</v>
+        <v>45.2</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>47.52</t>
+          <t>78.30</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>58.01</t>
+          <t>89.50</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；RSI=35.0超卖区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD金叉；MACD红柱放大；RSI=45.2中性区</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -813,46 +813,46 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>000333</t>
+          <t>601318</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>美的集团</t>
+          <t>中国平安</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>82.79</t>
+          <t>51.23</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>83.75</v>
+        <v>53.49</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>84.7</v>
+        <v>53.23</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>35.2</v>
+        <v>34.6</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78.30</t>
+          <t>48.47</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89.50</t>
+          <t>58.01</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=35.2中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；RSI=34.6超卖区</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -864,46 +864,46 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>510300</t>
+          <t>588000</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>沪深300ETF</t>
+          <t>科创50ETF</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>4.51</v>
+        <v>1.64</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>4.63</v>
+        <v>1.74</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>29.1</v>
+        <v>19.7</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=29.1超卖区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；RSI=19.7超卖区；近20日已跌-13.3%，接近超跌</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">

--- a/outputs/06_技术分析记录.xlsx
+++ b/outputs/06_技术分析记录.xlsx
@@ -507,7 +507,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -522,17 +522,17 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>29.98</t>
+          <t>29.38</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>31.14</v>
+        <v>30.89</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>32.09</v>
+        <v>32.1</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>35.2</v>
+        <v>38.7</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -546,7 +546,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=35.2中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；RSI=38.7中性区；近20日已跌-14.6%，接近超跌</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -558,7 +558,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -573,17 +573,17 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>29.45</t>
+          <t>29.60</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>28.54</v>
+        <v>28.62</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>28.4</v>
+        <v>28.43</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>68.5</v>
+        <v>70.2</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -592,12 +592,12 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>29.57</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=68.5中性区</t>
+          <t>均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=70.2中性区</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -609,97 +609,97 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>600036</t>
+          <t>300750</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>招商银行</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>42.67</t>
+          <t>278.50</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>41.29</v>
+        <v>301.52</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>39.99</v>
+        <v>353.24</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>69.5</v>
+        <v>32.3</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>272.00</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42.95</t>
+          <t>408.60</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=69.5中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；RSI=32.3超卖区；5日均量为60日均量的1.32倍，量能放大；近20日已跌-17.3%，接近超跌</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有</t>
+          <t>趋势中性，观望</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>300750</t>
+          <t>002475</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>立讯精密</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>280.12</t>
+          <t>44.65</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>304.44</v>
+        <v>50.84</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>354.79</v>
+        <v>55.02</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>32.5</v>
+        <v>23</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>280.12</t>
+          <t>43.56</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>408.60</t>
+          <t>64.20</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；RSI=32.5超卖区；近20日已跌-16.5%，接近超跌</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=23.0超卖区；近20日已跌-20.1%，接近超跌</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -711,109 +711,109 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>002475</t>
+          <t>600036</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>招商银行</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>44.94</t>
+          <t>42.66</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>51.4</v>
+        <v>41.38</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>55.28</v>
+        <v>40.07</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>22.3</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>44.70</t>
+          <t>37.50</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>64.20</t>
+          <t>42.95</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；RSI=22.3超卖区；近20日已跌-18.4%，接近超跌</t>
+          <t>均线多头排列(5&gt;10&gt;20&gt;60)；RSI=74.6中性区</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望</t>
+          <t>中期趋势向上，可关注/持有</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>000333</t>
+          <t>600519</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>美的集团</t>
+          <t>贵州茅台</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>83.70</t>
+          <t>1312.97</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>83.67</v>
+        <v>1265.32</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>84.73999999999999</v>
+        <v>1295.74</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>45.2</v>
+        <v>64.7</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>78.30</t>
+          <t>1228.10</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>89.50</t>
+          <t>1363.35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD金叉；MACD红柱放大；RSI=45.2中性区</t>
+          <t>价格站上60日均线；MACD红柱放大；RSI=64.7中性区</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望</t>
+          <t>中期趋势向上，可关注/持有</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -828,21 +828,21 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>51.23</t>
+          <t>51.78</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>53.49</v>
+        <v>53.32</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>53.23</v>
+        <v>53.26</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>34.6</v>
+        <v>39.9</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>48.47</t>
+          <t>49.26</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -852,7 +852,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；RSI=34.6超卖区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=39.9中性区</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -864,7 +864,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -879,31 +879,31 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>19.7</v>
+        <v>19.3</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；RSI=19.7超卖区；近20日已跌-13.3%，接近超跌</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；RSI=19.3超卖区；5日均量为60日均量的1.31倍，量能放大；近20日已跌-13.9%，接近超跌</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">

--- a/outputs/06_技术分析记录.xlsx
+++ b/outputs/06_技术分析记录.xlsx
@@ -507,7 +507,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -522,17 +522,17 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>29.38</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>30.89</v>
+        <v>30.68</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>32.1</v>
+        <v>32.12</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>38.7</v>
+        <v>39</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -546,7 +546,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；RSI=38.7中性区；近20日已跌-14.6%，接近超跌</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=39.0中性区；近20日已跌-12.3%，接近超跌</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -558,7 +558,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -573,21 +573,21 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>29.60</t>
+          <t>29.38</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>28.62</v>
+        <v>28.68</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>28.43</v>
+        <v>28.46</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>70.2</v>
+        <v>69.5</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>27.34</t>
+          <t>27.35</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -597,7 +597,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=70.2中性区</t>
+          <t>均线多头排列(5&gt;10&gt;20&gt;60)；RSI=69.5中性区</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -609,46 +609,46 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>300750</t>
+          <t>002475</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>立讯精密</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>278.50</t>
+          <t>44.67</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>301.52</v>
+        <v>50.35</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>353.24</v>
+        <v>54.74</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>32.3</v>
+        <v>10.4</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>272.00</t>
+          <t>43.56</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>408.60</t>
+          <t>63.02</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；RSI=32.3超卖区；5日均量为60日均量的1.32倍，量能放大；近20日已跌-17.3%，接近超跌</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=10.4超卖区；近20日已跌-18.0%，接近超跌</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -660,46 +660,46 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>002475</t>
+          <t>300750</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>44.65</t>
+          <t>277.00</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>50.84</v>
+        <v>298.47</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>55.02</v>
+        <v>351.78</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>23</v>
+        <v>32.6</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43.56</t>
+          <t>272.00</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64.20</t>
+          <t>408.60</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=23.0超卖区；近20日已跌-20.1%，接近超跌</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；RSI=32.6超卖区；近20日已跌-18.1%，接近超跌</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -711,7 +711,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -726,21 +726,21 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>42.66</t>
+          <t>42.45</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>41.38</v>
+        <v>41.42</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>40.07</v>
+        <v>40.15</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>74.59999999999999</v>
+        <v>71.2</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>37.50</t>
+          <t>37.63</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>均线多头排列(5&gt;10&gt;20&gt;60)；RSI=74.6中性区</t>
+          <t>均线多头排列(5&gt;10&gt;20&gt;60)；RSI=71.2中性区</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -762,7 +762,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -777,17 +777,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1312.97</t>
+          <t>1329.00</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1265.32</v>
+        <v>1267.52</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>1295.74</v>
+        <v>1296.91</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>64.7</v>
+        <v>72</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；MACD红柱放大；RSI=64.7中性区</t>
+          <t>价格站上60日均线；MACD红柱放大；RSI=72.0中性区</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -813,7 +813,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -828,21 +828,21 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>51.78</t>
+          <t>51.88</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>53.32</v>
+        <v>53.14</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>53.26</v>
+        <v>53.3</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>39.9</v>
+        <v>40.6</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>49.26</t>
+          <t>49.60</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -852,7 +852,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=39.9中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=40.6中性区</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -864,7 +864,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -879,17 +879,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>19.3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -898,12 +898,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；RSI=19.3超卖区；5日均量为60日均量的1.31倍，量能放大；近20日已跌-13.9%，接近超跌</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=8.7超卖区；近20日已跌-13.8%，接近超跌</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">

--- a/outputs/06_技术分析记录.xlsx
+++ b/outputs/06_技术分析记录.xlsx
@@ -507,7 +507,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -522,21 +522,21 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>29.92</t>
+          <t>29.79</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>30.68</v>
+        <v>30.55</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>32.12</v>
+        <v>32.15</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>39</v>
+        <v>38.8</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>27.50</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -546,7 +546,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=39.0中性区；近20日已跌-12.3%，接近超跌</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=38.8中性区</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -558,46 +558,46 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>600900</t>
+          <t>600036</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>长江电力</t>
+          <t>招商银行</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>29.38</t>
+          <t>43.05</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>28.68</v>
+        <v>41.51</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>28.46</v>
+        <v>40.24</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>69.5</v>
+        <v>72.2</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>27.35</t>
+          <t>37.63</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>43.16</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>均线多头排列(5&gt;10&gt;20&gt;60)；RSI=69.5中性区</t>
+          <t>均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=72.2中性区</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -624,17 +624,17 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>44.67</t>
+          <t>46.20</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>50.35</v>
+        <v>49.89</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>54.74</v>
+        <v>54.55</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>10.4</v>
+        <v>18.5</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -648,7 +648,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=10.4超卖区；近20日已跌-18.0%，接近超跌</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=18.5超卖区；近20日已跌-16.6%，接近超跌</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -660,7 +660,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -675,21 +675,21 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>277.00</t>
+          <t>267.02</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>298.47</v>
+        <v>295.3</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>351.78</v>
+        <v>350.25</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>32.6</v>
+        <v>30.5</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>272.00</t>
+          <t>267.02</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；RSI=32.6超卖区；近20日已跌-18.1%，接近超跌</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；RSI=30.5超卖区；近20日已跌-19.2%，接近超跌</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -711,46 +711,46 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>600036</t>
+          <t>000333</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>招商银行</t>
+          <t>美的集团</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>42.45</t>
+          <t>86.54</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>41.42</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>40.15</v>
+        <v>84.89</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>71.2</v>
+        <v>72.5</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>37.63</t>
+          <t>78.30</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>42.95</t>
+          <t>89.50</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>均线多头排列(5&gt;10&gt;20&gt;60)；RSI=71.2中性区</t>
+          <t>价格站上60日均线；MACD红柱放大；RSI=72.5中性区</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -762,109 +762,109 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>600519</t>
+          <t>600900</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>贵州茅台</t>
+          <t>长江电力</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1329.00</t>
+          <t>29.54</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1267.52</v>
+        <v>28.74</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>1296.91</v>
+        <v>28.49</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>72</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1228.10</t>
+          <t>27.51</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1363.35</t>
+          <t>29.80</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；MACD红柱放大；RSI=72.0中性区</t>
+          <t>均线多头排列(5&gt;10&gt;20&gt;60)；RSI=75.4超买区，短期回调风险</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有</t>
+          <t>趋势中性，观望</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>601318</t>
+          <t>600519</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>中国平安</t>
+          <t>贵州茅台</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>51.88</t>
+          <t>1324.97</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>53.14</v>
+        <v>1270.01</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>53.3</v>
+        <v>1298.11</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>40.6</v>
+        <v>72.3</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>49.60</t>
+          <t>1228.10</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>58.01</t>
+          <t>1363.35</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=40.6中性区</t>
+          <t>价格站上60日均线；MACD红柱放大；RSI=72.3中性区</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望</t>
+          <t>中期趋势向上，可关注/持有</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -879,17 +879,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>1.72</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>8.699999999999999</v>
+        <v>7</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=8.7超卖区；近20日已跌-13.8%，接近超跌</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=7.0超卖区；5日均量为60日均量的1.33倍，量能放大；近20日已跌-14.3%，接近超跌</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">

--- a/outputs/06_技术分析记录.xlsx
+++ b/outputs/06_技术分析记录.xlsx
@@ -507,7 +507,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -522,21 +522,21 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>29.79</t>
+          <t>29.06</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>30.55</v>
+        <v>30.39</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>32.15</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>38.8</v>
+        <v>34.1</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>28.55</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -546,7 +546,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=38.8中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；RSI=34.1超卖区</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -558,46 +558,46 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>600036</t>
+          <t>000333</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>招商银行</t>
+          <t>美的集团</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>43.05</t>
+          <t>85.28</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>41.51</v>
+        <v>83.47</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>40.24</v>
+        <v>84.91</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>72.2</v>
+        <v>61.3</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>37.63</t>
+          <t>78.30</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>43.16</t>
+          <t>89.50</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=72.2中性区</t>
+          <t>价格站上60日均线；MACD红柱放大；RSI=61.3中性区</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -624,17 +624,17 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>46.20</t>
+          <t>47.60</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>49.89</v>
+        <v>49.63</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>54.55</v>
+        <v>54.39</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>18.5</v>
+        <v>24.3</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -648,7 +648,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=18.5超卖区；近20日已跌-16.6%，接近超跌</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=24.3超卖区</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -660,211 +660,211 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>300750</t>
+          <t>600036</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>招商银行</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>267.02</t>
+          <t>42.52</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>295.3</v>
+        <v>41.54</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>350.25</v>
+        <v>40.3</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>30.5</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>267.02</t>
+          <t>37.63</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>408.60</t>
+          <t>43.16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；RSI=30.5超卖区；近20日已跌-19.2%，接近超跌</t>
+          <t>均线多头排列(5&gt;10&gt;20&gt;60)；RSI=67.6中性区</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望</t>
+          <t>中期趋势向上，可关注/持有</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>000333</t>
+          <t>600900</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>美的集团</t>
+          <t>长江电力</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>86.54</t>
+          <t>29.69</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>83.54000000000001</v>
+        <v>28.79</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>84.89</v>
+        <v>28.5</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>72.5</v>
+        <v>78.7</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>78.30</t>
+          <t>27.51</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>89.50</t>
+          <t>29.80</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；MACD红柱放大；RSI=72.5中性区</t>
+          <t>均线多头排列(5&gt;10&gt;20&gt;60)；RSI=78.7超买区，短期回调风险</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有</t>
+          <t>趋势中性，观望</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>600900</t>
+          <t>600519</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>长江电力</t>
+          <t>贵州茅台</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>29.54</t>
+          <t>1331.88</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>28.74</v>
+        <v>1272.7</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>28.49</v>
+        <v>1298.18</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>75.40000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27.51</t>
+          <t>1228.10</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29.80</t>
+          <t>1363.35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>均线多头排列(5&gt;10&gt;20&gt;60)；RSI=75.4超买区，短期回调风险</t>
+          <t>价格站上60日均线；MACD红柱放大；RSI=73.2中性区</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望</t>
+          <t>中期趋势向上，可关注/持有</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>600519</t>
+          <t>601318</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>贵州茅台</t>
+          <t>中国平安</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1324.97</t>
+          <t>51.20</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1270.01</v>
+        <v>52.8</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>1298.11</v>
+        <v>53.31</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>72.3</v>
+        <v>28.2</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1228.10</t>
+          <t>50.19</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1363.35</t>
+          <t>58.01</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；MACD红柱放大；RSI=72.3中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；RSI=28.2超卖区</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有</t>
+          <t>趋势中性，观望</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -879,21 +879,21 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=7.0超卖区；5日均量为60日均量的1.33倍，量能放大；近20日已跌-14.3%，接近超跌</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=7.7超卖区；5日均量为60日均量的1.44倍，量能放大；近20日已跌-12.2%，接近超跌</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">

--- a/outputs/06_技术分析记录.xlsx
+++ b/outputs/06_技术分析记录.xlsx
@@ -665,46 +665,46 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>600036</t>
+          <t>300750</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>招商银行</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>42.52</t>
+          <t>259.08</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>41.54</v>
+        <v>291.4</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>40.3</v>
+        <v>348.32</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>67.59999999999999</v>
+        <v>20.6</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37.63</t>
+          <t>254.55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43.16</t>
+          <t>408.60</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>均线多头排列(5&gt;10&gt;20&gt;60)；RSI=67.6中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD死叉；RSI=20.6超卖区；近20日已跌-23.1%，接近超跌</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有</t>
+          <t>趋势偏弱，回避或减仓</t>
         </is>
       </c>
     </row>
@@ -716,46 +716,46 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>600900</t>
+          <t>600036</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>长江电力</t>
+          <t>招商银行</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>29.69</t>
+          <t>42.52</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>28.79</v>
+        <v>41.54</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>28.5</v>
+        <v>40.3</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>78.7</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27.51</t>
+          <t>37.63</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29.80</t>
+          <t>43.16</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>均线多头排列(5&gt;10&gt;20&gt;60)；RSI=78.7超买区，短期回调风险</t>
+          <t>均线多头排列(5&gt;10&gt;20&gt;60)；RSI=67.6中性区</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望</t>
+          <t>中期趋势向上，可关注/持有</t>
         </is>
       </c>
     </row>
@@ -767,46 +767,46 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>600519</t>
+          <t>600900</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>贵州茅台</t>
+          <t>长江电力</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1331.88</t>
+          <t>29.69</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1272.7</v>
+        <v>28.79</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>1298.18</v>
+        <v>28.5</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>73.2</v>
+        <v>78.7</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1228.10</t>
+          <t>27.51</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1363.35</t>
+          <t>29.80</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；MACD红柱放大；RSI=73.2中性区</t>
+          <t>均线多头排列(5&gt;10&gt;20&gt;60)；RSI=78.7超买区，短期回调风险</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有</t>
+          <t>趋势中性，观望</t>
         </is>
       </c>
     </row>
@@ -818,46 +818,46 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>601318</t>
+          <t>600519</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>中国平安</t>
+          <t>贵州茅台</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>51.20</t>
+          <t>1331.88</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>52.8</v>
+        <v>1272.7</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>53.31</v>
+        <v>1298.18</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>28.2</v>
+        <v>73.2</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>50.19</t>
+          <t>1228.10</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>58.01</t>
+          <t>1363.35</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；RSI=28.2超卖区</t>
+          <t>价格站上60日均线；MACD红柱放大；RSI=73.2中性区</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望</t>
+          <t>中期趋势向上，可关注/持有</t>
         </is>
       </c>
     </row>

--- a/outputs/06_技术分析记录.xlsx
+++ b/outputs/06_技术分析记录.xlsx
@@ -507,46 +507,46 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>601899</t>
+          <t>300750</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>紫金矿业</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>29.06</t>
+          <t>227.90</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>30.39</v>
+        <v>286.97</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>32.15</v>
+        <v>345.77</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>34.1</v>
+        <v>15.2</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>28.55</t>
+          <t>227.08</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>35.47</t>
+          <t>408.60</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；RSI=34.1超卖区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；RSI=15.2超卖区；5日均量为60日均量的1.77倍，量能放大；近20日已跌-28.0%，接近超跌</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -558,58 +558,58 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>000333</t>
+          <t>601899</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>美的集团</t>
+          <t>紫金矿业</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>85.28</t>
+          <t>28.87</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>83.47</v>
+        <v>30.25</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>84.91</v>
+        <v>32.14</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>61.3</v>
+        <v>33.2</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>78.30</t>
+          <t>28.55</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>89.50</t>
+          <t>35.47</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；MACD红柱放大；RSI=61.3中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；RSI=33.2超卖区</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有</t>
+          <t>趋势中性，观望</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -624,17 +624,17 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>47.60</t>
+          <t>48.09</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>49.63</v>
+        <v>49.46</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>54.39</v>
+        <v>54.19</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>24.3</v>
+        <v>27.8</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -648,160 +648,160 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=24.3超卖区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD金叉；MACD红柱放大；RSI=27.8超卖区</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望</t>
+          <t>中期趋势向上，可关注/持有</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>300750</t>
+          <t>600036</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>招商银行</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>259.08</t>
+          <t>42.28</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>291.4</v>
+        <v>41.6</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>348.32</v>
+        <v>40.37</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>20.6</v>
+        <v>67.3</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>254.55</t>
+          <t>37.63</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>408.60</t>
+          <t>43.16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD死叉；RSI=20.6超卖区；近20日已跌-23.1%，接近超跌</t>
+          <t>均线多头排列(5&gt;10&gt;20&gt;60)；RSI=67.3中性区</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>趋势偏弱，回避或减仓</t>
+          <t>中期趋势向上，可关注/持有</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>600036</t>
+          <t>600900</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>招商银行</t>
+          <t>长江电力</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>42.52</t>
+          <t>29.57</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>41.54</v>
+        <v>28.84</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>40.3</v>
+        <v>28.52</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>67.59999999999999</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>37.63</t>
+          <t>27.51</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>43.16</t>
+          <t>29.80</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>均线多头排列(5&gt;10&gt;20&gt;60)；RSI=67.6中性区</t>
+          <t>均线多头排列(5&gt;10&gt;20&gt;60)；RSI=75.1超买区，短期回调风险</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有</t>
+          <t>趋势中性，观望</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>600900</t>
+          <t>601318</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>长江电力</t>
+          <t>中国平安</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>29.69</t>
+          <t>51.20</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>28.79</v>
+        <v>52.67</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>28.5</v>
+        <v>53.3</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>78.7</v>
+        <v>30.6</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27.51</t>
+          <t>50.19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29.80</t>
+          <t>58.01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>均线多头排列(5&gt;10&gt;20&gt;60)；RSI=78.7超买区，短期回调风险</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=30.6超卖区</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -813,7 +813,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -828,17 +828,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1331.88</t>
+          <t>1309.69</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1272.7</v>
+        <v>1274.55</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>1298.18</v>
+        <v>1298.21</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>73.2</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -852,19 +852,19 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；MACD红柱放大；RSI=73.2中性区</t>
+          <t>价格站上60日均线；RSI=65.6中性区</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有</t>
+          <t>趋势中性，观望</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -883,13 +883,13 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=7.7超卖区；5日均量为60日均量的1.44倍，量能放大；近20日已跌-12.2%，接近超跌</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=8.0超卖区；5日均量为60日均量的1.51倍，量能放大；近20日已跌-13.4%，接近超跌</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">

--- a/outputs/06_技术分析记录.xlsx
+++ b/outputs/06_技术分析记录.xlsx
@@ -507,46 +507,46 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>300750</t>
+          <t>601899</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>紫金矿业</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>227.90</t>
+          <t>27.84</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>286.97</v>
+        <v>30.04</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>345.77</v>
+        <v>32.07</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>15.2</v>
+        <v>35</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>227.08</t>
+          <t>27.50</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>408.60</t>
+          <t>35.47</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；RSI=15.2超卖区；5日均量为60日均量的1.77倍，量能放大；近20日已跌-28.0%，接近超跌</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；RSI=35.0超卖区；近20日已跌-13.5%，接近超跌</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -558,46 +558,46 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>601899</t>
+          <t>300750</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>紫金矿业</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>28.87</t>
+          <t>220.41</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>30.25</v>
+        <v>282.72</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>32.14</v>
+        <v>343.26</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>33.2</v>
+        <v>15.2</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>28.55</t>
+          <t>218.45</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>35.47</t>
+          <t>408.60</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；RSI=33.2超卖区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；RSI=15.2超卖区；5日均量为60日均量的2.01倍，量能放大；近20日已跌-27.8%，接近超跌</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -609,46 +609,46 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>002475</t>
+          <t>600900</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>长江电力</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>48.09</t>
+          <t>29.82</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>49.46</v>
+        <v>28.91</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>54.19</v>
+        <v>28.53</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>27.8</v>
+        <v>74.8</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>43.56</t>
+          <t>27.51</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>63.02</t>
+          <t>29.98</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD金叉；MACD红柱放大；RSI=27.8超卖区</t>
+          <t>均线多头排列(5&gt;10&gt;20&gt;60)；RSI=74.8中性区</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -660,46 +660,46 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>600036</t>
+          <t>000333</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>招商银行</t>
+          <t>美的集团</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>42.28</t>
+          <t>85.29</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>41.6</v>
+        <v>83.31</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>40.37</v>
+        <v>84.91</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>67.3</v>
+        <v>59</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37.63</t>
+          <t>78.30</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43.16</t>
+          <t>89.50</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>均线多头排列(5&gt;10&gt;20&gt;60)；RSI=67.3中性区</t>
+          <t>价格站上60日均线；MACD红柱放大；RSI=59.0中性区</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -711,46 +711,46 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>600900</t>
+          <t>002475</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>长江电力</t>
+          <t>立讯精密</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>29.57</t>
+          <t>47.01</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>28.84</v>
+        <v>49.06</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>28.52</v>
+        <v>53.88</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>75.09999999999999</v>
+        <v>30.8</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27.51</t>
+          <t>43.45</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29.80</t>
+          <t>62.91</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>均线多头排列(5&gt;10&gt;20&gt;60)；RSI=75.1超买区，短期回调风险</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=30.8超卖区</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -762,7 +762,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -777,17 +777,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>51.20</t>
+          <t>50.94</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>52.67</v>
+        <v>52.54</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>53.3</v>
+        <v>53.27</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>30.6</v>
+        <v>32.3</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=30.6超卖区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=32.3超卖区</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -813,7 +813,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -828,17 +828,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1309.69</t>
+          <t>1318.49</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1274.55</v>
+        <v>1277.57</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>1298.21</v>
+        <v>1298.43</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>65.59999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；RSI=65.6中性区</t>
+          <t>价格站上60日均线；RSI=72.3中性区</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -864,7 +864,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -879,14 +879,14 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>8</v>
@@ -898,12 +898,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=8.0超卖区；5日均量为60日均量的1.51倍，量能放大；近20日已跌-13.4%，接近超跌</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=8.0超卖区；5日均量为60日均量的1.49倍，量能放大；近20日已跌-19.4%，接近超跌</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">

--- a/outputs/06_技术分析记录.xlsx
+++ b/outputs/06_技术分析记录.xlsx
@@ -507,46 +507,46 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>601899</t>
+          <t>300750</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>紫金矿业</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>237.60</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>30.04</v>
+        <v>279.38</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>32.07</v>
+        <v>340.81</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>35</v>
+        <v>27.5</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>27.50</t>
+          <t>216.51</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>35.47</t>
+          <t>408.60</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；RSI=35.0超卖区；近20日已跌-13.5%，接近超跌</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=27.5超卖区；5日均量为60日均量的2.39倍，量能放大；近20日已跌-21.9%，接近超跌</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -558,46 +558,46 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>300750</t>
+          <t>601899</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>紫金矿业</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>220.41</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>282.72</v>
+        <v>29.93</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>343.26</v>
+        <v>32.01</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>15.2</v>
+        <v>45.8</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>218.45</t>
+          <t>26.60</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>408.60</t>
+          <t>35.47</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；RSI=15.2超卖区；5日均量为60日均量的2.01倍，量能放大；近20日已跌-27.8%，接近超跌</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=45.8中性区</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -624,17 +624,17 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>29.82</t>
+          <t>29.45</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>28.91</v>
+        <v>28.96</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>28.53</v>
+        <v>28.54</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>74.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -643,12 +643,12 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29.98</t>
+          <t>29.99</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>均线多头排列(5&gt;10&gt;20&gt;60)；RSI=74.8中性区</t>
+          <t>均线多头排列(5&gt;10&gt;20&gt;60)；RSI=64.4中性区</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -660,7 +660,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -675,17 +675,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>85.29</t>
+          <t>85.59</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>83.31</v>
+        <v>83.34</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>84.91</v>
+        <v>84.92</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>59</v>
+        <v>62.5</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -699,7 +699,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；MACD红柱放大；RSI=59.0中性区</t>
+          <t>价格站上60日均线；MACD红柱放大；RSI=62.5中性区</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -711,97 +711,97 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>002475</t>
+          <t>600519</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>贵州茅台</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>47.01</t>
+          <t>1335.00</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>49.06</v>
+        <v>1280.97</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>53.88</v>
+        <v>1299.15</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>30.8</v>
+        <v>73.7</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>43.45</t>
+          <t>1228.10</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>62.91</t>
+          <t>1363.35</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=30.8超卖区</t>
+          <t>价格站上60日均线；MACD红柱放大；RSI=73.7中性区</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望</t>
+          <t>中期趋势向上，可关注/持有</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>601318</t>
+          <t>002475</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>中国平安</t>
+          <t>立讯精密</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>50.94</t>
+          <t>50.42</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>52.54</v>
+        <v>48.98</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>53.27</v>
+        <v>53.7</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>32.3</v>
+        <v>52.2</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>50.19</t>
+          <t>43.45</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>58.01</t>
+          <t>62.91</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=32.3超卖区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=52.2中性区</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -813,46 +813,46 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>600519</t>
+          <t>600036</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>贵州茅台</t>
+          <t>招商银行</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1318.49</t>
+          <t>41.77</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1277.57</v>
+        <v>41.7</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>1298.43</v>
+        <v>40.47</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>72.3</v>
+        <v>60.8</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1228.10</t>
+          <t>38.03</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1363.35</t>
+          <t>43.16</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；RSI=72.3中性区</t>
+          <t>价格站上60日均线；RSI=60.8中性区</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -864,7 +864,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -879,31 +879,31 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>8</v>
+        <v>20.5</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=8.0超卖区；5日均量为60日均量的1.49倍，量能放大；近20日已跌-19.4%，接近超跌</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=20.5超卖区；5日均量为60日均量的1.67倍，量能放大；近20日已跌-16.2%，接近超跌</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">

--- a/outputs/06_技术分析记录.xlsx
+++ b/outputs/06_技术分析记录.xlsx
@@ -507,7 +507,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -522,17 +522,17 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>237.60</t>
+          <t>238.00</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>279.38</v>
+        <v>276.19</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>340.81</v>
+        <v>338.42</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>27.5</v>
+        <v>28.9</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -546,7 +546,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=27.5超卖区；5日均量为60日均量的2.39倍，量能放大；近20日已跌-21.9%，接近超跌</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=28.9超卖区；5日均量为60日均量的2.52倍，量能放大；近20日已跌-21.2%，接近超跌</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -558,7 +558,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -573,17 +573,17 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>27.47</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>29.93</v>
+        <v>29.73</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>32.01</v>
+        <v>31.95</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>45.8</v>
+        <v>38.8</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -597,7 +597,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=45.8中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；RSI=38.8中性区；近20日已跌-12.5%，接近超跌</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -624,17 +624,17 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>29.45</t>
+          <t>29.86</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>28.96</v>
+        <v>29.04</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>28.54</v>
+        <v>28.55</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>64.40000000000001</v>
+        <v>72</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -648,7 +648,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>均线多头排列(5&gt;10&gt;20&gt;60)；RSI=64.4中性区</t>
+          <t>均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=72.0中性区</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -660,46 +660,46 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>000333</t>
+          <t>600036</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>美的集团</t>
+          <t>招商银行</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>85.59</t>
+          <t>42.50</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>83.34</v>
+        <v>41.8</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>84.92</v>
+        <v>40.52</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>62.5</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78.30</t>
+          <t>38.03</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89.50</t>
+          <t>43.16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；MACD红柱放大；RSI=62.5中性区</t>
+          <t>价格站上60日均线；MACD红柱放大；RSI=67.1中性区</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -711,58 +711,58 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>600519</t>
+          <t>000333</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>贵州茅台</t>
+          <t>美的集团</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1335.00</t>
+          <t>85.50</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1280.97</v>
+        <v>83.39</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>1299.15</v>
+        <v>84.94</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>73.7</v>
+        <v>63.6</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1228.10</t>
+          <t>78.30</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1363.35</t>
+          <t>89.50</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；MACD红柱放大；RSI=73.7中性区</t>
+          <t>价格站上60日均线；RSI=63.6中性区</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有</t>
+          <t>趋势中性，观望</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -777,17 +777,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>50.42</t>
+          <t>49.81</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>48.98</v>
+        <v>48.77</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>53.7</v>
+        <v>53.52</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>52.2</v>
+        <v>48.3</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=52.2中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=48.3中性区</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -813,46 +813,46 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>600036</t>
+          <t>601318</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>招商银行</t>
+          <t>中国平安</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>41.77</t>
+          <t>52.62</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>41.7</v>
+        <v>52.42</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>40.47</v>
+        <v>53.23</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>60.8</v>
+        <v>50.8</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>38.03</t>
+          <t>50.11</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>43.16</t>
+          <t>58.01</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；RSI=60.8中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=50.8中性区</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -864,7 +864,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -879,17 +879,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>20.5</v>
+        <v>15.7</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -898,12 +898,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=20.5超卖区；5日均量为60日均量的1.67倍，量能放大；近20日已跌-16.2%，接近超跌</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=15.7超卖区；5日均量为60日均量的1.78倍，量能放大；近20日已跌-20.8%，接近超跌</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">

--- a/outputs/06_技术分析记录.xlsx
+++ b/outputs/06_技术分析记录.xlsx
@@ -507,7 +507,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -522,17 +522,17 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>238.00</t>
+          <t>233.00</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>276.19</v>
+        <v>272.98</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>338.42</v>
+        <v>335.66</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>28.9</v>
+        <v>25.1</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -546,7 +546,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=28.9超卖区；5日均量为60日均量的2.52倍，量能放大；近20日已跌-21.2%，接近超跌</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=25.1超卖区；5日均量为60日均量的2.42倍，量能放大；近20日已跌-21.6%，接近超跌</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -558,7 +558,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -573,17 +573,17 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>27.47</t>
+          <t>27.85</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>29.73</v>
+        <v>29.56</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>31.95</v>
+        <v>31.89</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>38.8</v>
+        <v>39.1</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -597,7 +597,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；RSI=38.8中性区；近20日已跌-12.5%，接近超跌</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=39.1中性区</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -624,17 +624,17 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>29.86</t>
+          <t>29.83</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>29.04</v>
+        <v>29.13</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>28.55</v>
+        <v>28.58</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -648,7 +648,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=72.0中性区</t>
+          <t>均线多头排列(5&gt;10&gt;20&gt;60)；RSI=70.0中性区</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -660,148 +660,148 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>600036</t>
+          <t>601318</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>招商银行</t>
+          <t>中国平安</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>42.50</t>
+          <t>52.61</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>41.8</v>
+        <v>52.35</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>40.52</v>
+        <v>53.24</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>67.09999999999999</v>
+        <v>44.8</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38.03</t>
+          <t>50.11</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43.16</t>
+          <t>58.01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；MACD红柱放大；RSI=67.1中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD金叉；MACD红柱放大；RSI=44.8中性区</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有</t>
+          <t>趋势中性，观望</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>000333</t>
+          <t>600036</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>美的集团</t>
+          <t>招商银行</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>85.50</t>
+          <t>42.99</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>83.39</v>
+        <v>41.9</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>84.94</v>
+        <v>40.59</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>63.6</v>
+        <v>65.5</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>78.30</t>
+          <t>38.03</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>89.50</t>
+          <t>43.16</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；RSI=63.6中性区</t>
+          <t>价格站上60日均线；MACD红柱放大；RSI=65.5中性区</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望</t>
+          <t>中期趋势向上，可关注/持有</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>002475</t>
+          <t>000333</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>美的集团</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>49.81</t>
+          <t>85.04</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>48.77</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>53.52</v>
+        <v>84.95</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>48.3</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>43.45</t>
+          <t>78.30</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>62.91</t>
+          <t>89.50</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=48.3中性区</t>
+          <t>价格站上60日均线；RSI=68.9中性区</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -813,46 +813,46 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>601318</t>
+          <t>002475</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>中国平安</t>
+          <t>立讯精密</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>52.62</t>
+          <t>48.80</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>52.42</v>
+        <v>48.49</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>53.23</v>
+        <v>53.29</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>50.8</v>
+        <v>48.2</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>50.11</t>
+          <t>43.45</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>58.01</t>
+          <t>62.57</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=50.8中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=48.2中性区</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -864,46 +864,46 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>588000</t>
+          <t>510300</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>科创50ETF</t>
+          <t>沪深300ETF</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1.54</v>
+        <v>4.32</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>1.67</v>
+        <v>4.54</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>15.7</v>
+        <v>16.5</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>4.80</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=15.7超卖区；5日均量为60日均量的1.78倍，量能放大；近20日已跌-20.8%，接近超跌</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=16.5超卖区；5日均量为60日均量的2.33倍，量能放大</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">

--- a/outputs/06_技术分析记录.xlsx
+++ b/outputs/06_技术分析记录.xlsx
@@ -507,7 +507,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -522,17 +522,17 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>233.00</t>
+          <t>229.14</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>272.98</v>
+        <v>269.21</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>335.66</v>
+        <v>332.99</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>25.1</v>
+        <v>25.2</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -546,7 +546,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=25.1超卖区；5日均量为60日均量的2.42倍，量能放大；近20日已跌-21.6%，接近超跌</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=25.2超卖区；5日均量为60日均量的1.89倍，量能放大；近20日已跌-24.8%，接近超跌</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -558,7 +558,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -573,17 +573,17 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>27.85</t>
+          <t>27.95</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>29.56</v>
+        <v>29.39</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>31.89</v>
+        <v>31.83</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>39.1</v>
+        <v>41.7</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -597,7 +597,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=39.1中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=41.7中性区</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -624,17 +624,17 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>29.83</t>
+          <t>29.40</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>29.13</v>
+        <v>29.2</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>28.58</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>70</v>
+        <v>57.6</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -648,7 +648,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>均线多头排列(5&gt;10&gt;20&gt;60)；RSI=70.0中性区</t>
+          <t>均线多头排列(5&gt;10&gt;20&gt;60)；RSI=57.6中性区；5日均量为60日均量的1.39倍，量能放大</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -660,97 +660,97 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>601318</t>
+          <t>600276</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>中国平安</t>
+          <t>恒瑞医药</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>52.61</t>
+          <t>48.36</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>52.35</v>
+        <v>46.34</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>53.24</v>
+        <v>47.95</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>44.8</v>
+        <v>56</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50.11</t>
+          <t>41.89</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>58.01</t>
+          <t>55.88</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD金叉；MACD红柱放大；RSI=44.8中性区</t>
+          <t>价格站上60日均线；MACD红柱放大；RSI=56.0中性区</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望</t>
+          <t>中期趋势向上，可关注/持有</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>600036</t>
+          <t>000333</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>招商银行</t>
+          <t>美的集团</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>42.99</t>
+          <t>85.91</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>41.9</v>
+        <v>83.77</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>40.59</v>
+        <v>84.95999999999999</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>65.5</v>
+        <v>67</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>38.03</t>
+          <t>78.30</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>43.16</t>
+          <t>89.50</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；MACD红柱放大；RSI=65.5中性区</t>
+          <t>价格站上60日均线；MACD红柱放大；RSI=67.0中性区</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -762,58 +762,58 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>000333</t>
+          <t>600036</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>美的集团</t>
+          <t>招商银行</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>85.04</t>
+          <t>42.13</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>83.59999999999999</v>
+        <v>41.96</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>84.95</v>
+        <v>40.63</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>68.90000000000001</v>
+        <v>53.5</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>78.30</t>
+          <t>38.03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>89.50</t>
+          <t>43.16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；RSI=68.9中性区</t>
+          <t>价格站上60日均线；RSI=53.5中性区；5日均量为60日均量的1.34倍，量能放大</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望</t>
+          <t>中期趋势向上，可关注/持有</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -828,17 +828,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>48.80</t>
+          <t>49.70</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>48.49</v>
+        <v>48.24</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>53.29</v>
+        <v>53.12</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>48.2</v>
+        <v>54.9</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -847,12 +847,12 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>62.57</t>
+          <t>62.39</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=48.2中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=54.9中性区</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -864,46 +864,46 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>510300</t>
+          <t>588000</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>沪深300ETF</t>
+          <t>科创50ETF</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>4.32</v>
+        <v>1.49</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>4.54</v>
+        <v>1.66</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>16.5</v>
+        <v>25.7</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4.80</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=16.5超卖区；5日均量为60日均量的2.33倍，量能放大</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=25.7超卖区；5日均量为60日均量的1.80倍，量能放大；近20日已跌-23.0%，接近超跌</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">

--- a/outputs/06_技术分析记录.xlsx
+++ b/outputs/06_技术分析记录.xlsx
@@ -507,7 +507,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -522,17 +522,17 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>229.14</t>
+          <t>229.07</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>269.21</v>
+        <v>265.61</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>332.99</v>
+        <v>330.21</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>25.2</v>
+        <v>17.3</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -546,7 +546,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=25.2超卖区；5日均量为60日均量的1.89倍，量能放大；近20日已跌-24.8%，接近超跌</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=17.3超卖区；5日均量为60日均量的1.60倍，量能放大；近20日已跌-23.9%，接近超跌</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -558,7 +558,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -573,17 +573,17 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>27.95</t>
+          <t>28.04</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>29.39</v>
+        <v>29.22</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>31.83</v>
+        <v>31.77</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>41.7</v>
+        <v>30.9</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -597,7 +597,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=41.7中性区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=30.9超卖区</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -624,17 +624,17 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>29.40</t>
+          <t>29.99</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>29.2</v>
+        <v>29.29</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>28.58</v>
+        <v>28.6</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>57.6</v>
+        <v>63.2</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -648,7 +648,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>均线多头排列(5&gt;10&gt;20&gt;60)；RSI=57.6中性区；5日均量为60日均量的1.39倍，量能放大</t>
+          <t>均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=63.2中性区；5日均量为60日均量的1.37倍，量能放大</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -660,7 +660,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -675,17 +675,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>48.36</t>
+          <t>48.62</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>46.34</v>
+        <v>46.49</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>47.95</v>
+        <v>47.86</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>56</v>
+        <v>57.7</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -699,7 +699,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；MACD红柱放大；RSI=56.0中性区</t>
+          <t>价格站上60日均线；MACD红柱放大；RSI=57.7中性区</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -711,46 +711,46 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>000333</t>
+          <t>600036</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>美的集团</t>
+          <t>招商银行</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>85.91</t>
+          <t>42.94</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>83.77</v>
+        <v>42.08</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>84.95999999999999</v>
+        <v>40.68</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>67</v>
+        <v>61.7</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>78.30</t>
+          <t>38.03</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>89.50</t>
+          <t>43.16</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；MACD红柱放大；RSI=67.0中性区</t>
+          <t>均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=61.7中性区；5日均量为60日均量的1.36倍，量能放大</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -762,46 +762,46 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>600036</t>
+          <t>000333</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>招商银行</t>
+          <t>美的集团</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>42.13</t>
+          <t>87.48</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>41.96</v>
+        <v>84.02</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>40.63</v>
+        <v>84.97</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>53.5</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>38.03</t>
+          <t>78.30</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43.16</t>
+          <t>89.50</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；RSI=53.5中性区；5日均量为60日均量的1.34倍，量能放大</t>
+          <t>价格站上60日均线；MACD红柱放大；RSI=69.1中性区</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -813,97 +813,97 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>002475</t>
+          <t>600519</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>贵州茅台</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>49.70</t>
+          <t>1354.00</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>48.24</v>
+        <v>1299.77</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>53.12</v>
+        <v>1301.86</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>54.9</v>
+        <v>70.7</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>43.45</t>
+          <t>1228.10</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>62.39</t>
+          <t>1363.35</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=54.9中性区</t>
+          <t>价格站上60日均线；RSI=70.7中性区；5日均量为60日均量的1.31倍，量能放大</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望</t>
+          <t>中期趋势向上，可关注/持有</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>588000</t>
+          <t>510300</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>科创50ETF</t>
+          <t>沪深300ETF</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1.49</v>
+        <v>4.28</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>1.66</v>
+        <v>4.53</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>25.7</v>
+        <v>21.7</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>4.80</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=25.7超卖区；5日均量为60日均量的1.80倍，量能放大；近20日已跌-23.0%，接近超跌</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=21.7超卖区；5日均量为60日均量的2.00倍，量能放大</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">

--- a/outputs/06_技术分析记录.xlsx
+++ b/outputs/06_技术分析记录.xlsx
@@ -507,58 +507,58 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>300750</t>
+          <t>600036</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>招商银行</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>229.07</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>265.61</v>
+        <v>42.22</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>330.21</v>
+        <v>40.73</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>17.3</v>
+        <v>56.8</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>216.51</t>
+          <t>38.03</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>408.60</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=17.3超卖区；5日均量为60日均量的1.60倍，量能放大；近20日已跌-23.9%，接近超跌</t>
+          <t>均线多头排列(5&gt;10&gt;20&gt;60)；MACD金叉；MACD红柱放大；RSI=56.8中性区；5日均量为60日均量的1.32倍，量能放大</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望</t>
+          <t>中期趋势向上，可关注/持有</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -573,17 +573,17 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>28.04</t>
+          <t>27.62</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>29.22</v>
+        <v>29.1</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>31.77</v>
+        <v>31.69</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>30.9</v>
+        <v>31.6</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -597,7 +597,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=30.9超卖区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=31.6超卖区</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -609,58 +609,58 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>600900</t>
+          <t>300750</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>长江电力</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>29.99</t>
+          <t>233.37</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>29.29</v>
+        <v>262.6</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>28.6</v>
+        <v>327.43</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>63.2</v>
+        <v>20.1</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27.51</t>
+          <t>216.51</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29.99</t>
+          <t>408.60</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=63.2中性区；5日均量为60日均量的1.37倍，量能放大</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=20.1超卖区；近20日已跌-20.5%，接近超跌</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有</t>
+          <t>趋势中性，观望</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -675,17 +675,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>48.62</t>
+          <t>48.46</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>46.49</v>
+        <v>46.67</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>47.86</v>
+        <v>47.76</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>57.7</v>
+        <v>61.2</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -699,7 +699,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；MACD红柱放大；RSI=57.7中性区</t>
+          <t>价格站上60日均线；MACD红柱放大；RSI=61.2中性区</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -711,46 +711,46 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>600036</t>
+          <t>000333</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>招商银行</t>
+          <t>美的集团</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>42.94</t>
+          <t>89.11</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>42.08</v>
+        <v>84.34</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>40.68</v>
+        <v>84.97</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>61.7</v>
+        <v>70.5</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>38.03</t>
+          <t>78.30</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>43.16</t>
+          <t>89.49</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=61.7中性区；5日均量为60日均量的1.36倍，量能放大</t>
+          <t>价格站上60日均线；MACD红柱放大；RSI=70.5中性区</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -762,46 +762,46 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>000333</t>
+          <t>600519</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>美的集团</t>
+          <t>贵州茅台</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>87.48</t>
+          <t>1392.05</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>84.02</v>
+        <v>1307.52</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>84.97</v>
+        <v>1302.37</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>69.09999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>78.30</t>
+          <t>1228.10</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>89.50</t>
+          <t>1393.37</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；MACD红柱放大；RSI=69.1中性区</t>
+          <t>均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=72.3中性区；5日均量为60日均量的1.34倍，量能放大；近20日已涨12.5%，短期涨幅过大</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -813,97 +813,97 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>600519</t>
+          <t>002475</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>贵州茅台</t>
+          <t>立讯精密</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1354.00</t>
+          <t>45.60</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1299.77</v>
+        <v>47.62</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>1301.86</v>
+        <v>52.67</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>70.7</v>
+        <v>48.1</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1228.10</t>
+          <t>43.45</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1363.35</t>
+          <t>60.72</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；RSI=70.7中性区；5日均量为60日均量的1.31倍，量能放大</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；RSI=48.1中性区；近20日已跌-12.1%，接近超跌</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有</t>
+          <t>趋势中性，观望</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>510300</t>
+          <t>588000</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>沪深300ETF</t>
+          <t>科创50ETF</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>4.28</v>
+        <v>1.45</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>4.53</v>
+        <v>1.64</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>21.7</v>
+        <v>20.1</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4.80</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=21.7超卖区；5日均量为60日均量的2.00倍，量能放大</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；RSI=20.1超卖区；5日均量为60日均量的1.67倍，量能放大；近20日已跌-28.2%，接近超跌</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">

--- a/outputs/06_技术分析记录.xlsx
+++ b/outputs/06_技术分析记录.xlsx
@@ -573,7 +573,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>27.62</t>
+          <t>27.60</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -583,7 +583,7 @@
         <v>31.69</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>31.6</v>
+        <v>31.5</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -597,7 +597,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=31.6超卖区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=31.5超卖区</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -624,17 +624,17 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>233.37</t>
+          <t>232.92</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>262.6</v>
+        <v>262.58</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>327.43</v>
+        <v>327.42</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>20.1</v>
+        <v>19.8</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -648,7 +648,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=20.1超卖区；近20日已跌-20.5%，接近超跌</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=19.8超卖区；近20日已跌-20.6%，接近超跌</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -726,17 +726,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>89.11</t>
+          <t>89.18</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>84.34</v>
+        <v>84.34999999999999</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>84.97</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>70.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；MACD红柱放大；RSI=70.5中性区</t>
+          <t>价格站上60日均线；MACD红柱放大；RSI=70.6中性区</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -889,7 +889,7 @@
         <v>1.64</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；RSI=20.1超卖区；5日均量为60日均量的1.67倍，量能放大；近20日已跌-28.2%，接近超跌</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；RSI=20.0超卖区；5日均量为60日均量的1.67倍，量能放大；近20日已跌-28.3%，接近超跌</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
